--- a/table/osmr.xlsx
+++ b/table/osmr.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10315"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annabethlu/R_Projects/ded-dep-ibs/table/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annabethlu/Projects/ded-dep-ibs/table/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DF4B31E-ECE7-4247-B72F-07FF923C5911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="18400" firstSheet="29" activeTab="31" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="980" yWindow="720" windowWidth="28420" windowHeight="18400" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="one sample MR" sheetId="1" r:id="rId1"/>
@@ -2162,10 +2162,31 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2174,22 +2195,28 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2205,33 +2232,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2307,8 +2307,8 @@
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>4267695</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>199407</xdr:rowOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>1333</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5501,16 +5501,16 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="54" t="s">
+      <c r="B1" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="55" t="s">
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="55"/>
-      <c r="G1" s="56"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="55"/>
       <c r="H1" s="2" t="s">
         <v>55</v>
       </c>
@@ -5537,25 +5537,25 @@
       </c>
     </row>
     <row r="2" spans="1:15">
-      <c r="A2" s="60" t="s">
+      <c r="A2" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="45" t="s">
+      <c r="C2" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="47" t="s">
+      <c r="D2" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="41" t="s">
+      <c r="E2" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="41" t="s">
+      <c r="F2" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="39" t="s">
+      <c r="G2" s="56" t="s">
         <v>14</v>
       </c>
       <c r="H2" s="33" t="s">
@@ -5584,13 +5584,13 @@
       </c>
     </row>
     <row r="3" spans="1:15">
-      <c r="A3" s="61"/>
-      <c r="B3" s="44"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="40"/>
+      <c r="A3" s="51"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="57"/>
       <c r="H3" s="31" t="s">
         <v>16</v>
       </c>
@@ -5617,13 +5617,13 @@
       </c>
     </row>
     <row r="4" spans="1:15">
-      <c r="A4" s="61"/>
-      <c r="B4" s="44"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="42"/>
-      <c r="F4" s="42"/>
-      <c r="G4" s="40"/>
+      <c r="A4" s="51"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="57"/>
       <c r="H4" s="31" t="s">
         <v>17</v>
       </c>
@@ -5650,13 +5650,13 @@
       </c>
     </row>
     <row r="5" spans="1:15">
-      <c r="A5" s="61"/>
-      <c r="B5" s="44"/>
-      <c r="C5" s="46"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="42"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="40"/>
+      <c r="A5" s="51"/>
+      <c r="B5" s="40"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="46"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="57"/>
       <c r="H5" s="31" t="s">
         <v>18</v>
       </c>
@@ -5683,13 +5683,13 @@
       </c>
     </row>
     <row r="6" spans="1:15">
-      <c r="A6" s="61"/>
-      <c r="B6" s="44"/>
-      <c r="C6" s="46"/>
-      <c r="D6" s="48"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="40"/>
+      <c r="A6" s="51"/>
+      <c r="B6" s="40"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="46"/>
+      <c r="E6" s="49"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="57"/>
       <c r="H6" s="31" t="s">
         <v>19</v>
       </c>
@@ -5716,13 +5716,13 @@
       </c>
     </row>
     <row r="7" spans="1:15">
-      <c r="A7" s="61"/>
-      <c r="B7" s="44"/>
-      <c r="C7" s="46"/>
-      <c r="D7" s="48"/>
-      <c r="E7" s="42"/>
-      <c r="F7" s="42"/>
-      <c r="G7" s="40"/>
+      <c r="A7" s="51"/>
+      <c r="B7" s="40"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="57"/>
       <c r="H7" s="31" t="s">
         <v>20</v>
       </c>
@@ -5749,13 +5749,13 @@
       </c>
     </row>
     <row r="8" spans="1:15">
-      <c r="A8" s="61"/>
-      <c r="B8" s="44"/>
-      <c r="C8" s="46"/>
-      <c r="D8" s="48"/>
-      <c r="E8" s="42"/>
-      <c r="F8" s="42"/>
-      <c r="G8" s="40"/>
+      <c r="A8" s="51"/>
+      <c r="B8" s="40"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="49"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="57"/>
       <c r="H8" s="32" t="s">
         <v>21</v>
       </c>
@@ -5782,13 +5782,13 @@
       </c>
     </row>
     <row r="9" spans="1:15">
-      <c r="A9" s="61"/>
-      <c r="B9" s="44"/>
-      <c r="C9" s="46"/>
-      <c r="D9" s="48"/>
-      <c r="E9" s="42"/>
-      <c r="F9" s="42"/>
-      <c r="G9" s="40"/>
+      <c r="A9" s="51"/>
+      <c r="B9" s="40"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="46"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="57"/>
       <c r="H9" s="31" t="s">
         <v>22</v>
       </c>
@@ -5815,13 +5815,13 @@
       </c>
     </row>
     <row r="10" spans="1:15" ht="17" thickBot="1">
-      <c r="A10" s="61"/>
-      <c r="B10" s="44"/>
-      <c r="C10" s="46"/>
-      <c r="D10" s="48"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
-      <c r="G10" s="40"/>
+      <c r="A10" s="51"/>
+      <c r="B10" s="40"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="49"/>
+      <c r="F10" s="49"/>
+      <c r="G10" s="57"/>
       <c r="H10" s="34" t="s">
         <v>23</v>
       </c>
@@ -5848,23 +5848,23 @@
       </c>
     </row>
     <row r="11" spans="1:15">
-      <c r="A11" s="61"/>
-      <c r="B11" s="43" t="s">
+      <c r="A11" s="51"/>
+      <c r="B11" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="45" t="s">
+      <c r="C11" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="47" t="s">
+      <c r="D11" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="41" t="s">
+      <c r="E11" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="41" t="s">
+      <c r="F11" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="G11" s="39" t="s">
+      <c r="G11" s="56" t="s">
         <v>56</v>
       </c>
       <c r="H11" s="33" t="s">
@@ -5893,13 +5893,13 @@
       </c>
     </row>
     <row r="12" spans="1:15">
-      <c r="A12" s="61"/>
-      <c r="B12" s="44"/>
-      <c r="C12" s="46"/>
-      <c r="D12" s="48"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="40"/>
+      <c r="A12" s="51"/>
+      <c r="B12" s="40"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="46"/>
+      <c r="E12" s="49"/>
+      <c r="F12" s="49"/>
+      <c r="G12" s="57"/>
       <c r="H12" s="31" t="s">
         <v>16</v>
       </c>
@@ -5926,13 +5926,13 @@
       </c>
     </row>
     <row r="13" spans="1:15">
-      <c r="A13" s="61"/>
-      <c r="B13" s="44"/>
-      <c r="C13" s="46"/>
-      <c r="D13" s="48"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="42"/>
-      <c r="G13" s="40"/>
+      <c r="A13" s="51"/>
+      <c r="B13" s="40"/>
+      <c r="C13" s="43"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="49"/>
+      <c r="F13" s="49"/>
+      <c r="G13" s="57"/>
       <c r="H13" s="31" t="s">
         <v>17</v>
       </c>
@@ -5959,13 +5959,13 @@
       </c>
     </row>
     <row r="14" spans="1:15">
-      <c r="A14" s="61"/>
-      <c r="B14" s="44"/>
-      <c r="C14" s="46"/>
-      <c r="D14" s="48"/>
-      <c r="E14" s="42"/>
-      <c r="F14" s="42"/>
-      <c r="G14" s="40"/>
+      <c r="A14" s="51"/>
+      <c r="B14" s="40"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="46"/>
+      <c r="E14" s="49"/>
+      <c r="F14" s="49"/>
+      <c r="G14" s="57"/>
       <c r="H14" s="31" t="s">
         <v>18</v>
       </c>
@@ -5992,13 +5992,13 @@
       </c>
     </row>
     <row r="15" spans="1:15">
-      <c r="A15" s="61"/>
-      <c r="B15" s="44"/>
-      <c r="C15" s="46"/>
-      <c r="D15" s="48"/>
-      <c r="E15" s="42"/>
-      <c r="F15" s="42"/>
-      <c r="G15" s="40"/>
+      <c r="A15" s="51"/>
+      <c r="B15" s="40"/>
+      <c r="C15" s="43"/>
+      <c r="D15" s="46"/>
+      <c r="E15" s="49"/>
+      <c r="F15" s="49"/>
+      <c r="G15" s="57"/>
       <c r="H15" s="32" t="s">
         <v>19</v>
       </c>
@@ -6025,13 +6025,13 @@
       </c>
     </row>
     <row r="16" spans="1:15">
-      <c r="A16" s="61"/>
-      <c r="B16" s="44"/>
-      <c r="C16" s="46"/>
-      <c r="D16" s="48"/>
-      <c r="E16" s="42"/>
-      <c r="F16" s="42"/>
-      <c r="G16" s="40"/>
+      <c r="A16" s="51"/>
+      <c r="B16" s="40"/>
+      <c r="C16" s="43"/>
+      <c r="D16" s="46"/>
+      <c r="E16" s="49"/>
+      <c r="F16" s="49"/>
+      <c r="G16" s="57"/>
       <c r="H16" s="31" t="s">
         <v>20</v>
       </c>
@@ -6058,13 +6058,13 @@
       </c>
     </row>
     <row r="17" spans="1:15">
-      <c r="A17" s="61"/>
-      <c r="B17" s="44"/>
-      <c r="C17" s="46"/>
-      <c r="D17" s="48"/>
-      <c r="E17" s="42"/>
-      <c r="F17" s="42"/>
-      <c r="G17" s="40"/>
+      <c r="A17" s="51"/>
+      <c r="B17" s="40"/>
+      <c r="C17" s="43"/>
+      <c r="D17" s="46"/>
+      <c r="E17" s="49"/>
+      <c r="F17" s="49"/>
+      <c r="G17" s="57"/>
       <c r="H17" s="31" t="s">
         <v>21</v>
       </c>
@@ -6091,13 +6091,13 @@
       </c>
     </row>
     <row r="18" spans="1:15">
-      <c r="A18" s="61"/>
-      <c r="B18" s="44"/>
-      <c r="C18" s="46"/>
-      <c r="D18" s="48"/>
-      <c r="E18" s="42"/>
-      <c r="F18" s="42"/>
-      <c r="G18" s="40"/>
+      <c r="A18" s="51"/>
+      <c r="B18" s="40"/>
+      <c r="C18" s="43"/>
+      <c r="D18" s="46"/>
+      <c r="E18" s="49"/>
+      <c r="F18" s="49"/>
+      <c r="G18" s="57"/>
       <c r="H18" s="31" t="s">
         <v>22</v>
       </c>
@@ -6124,13 +6124,13 @@
       </c>
     </row>
     <row r="19" spans="1:15" ht="17" thickBot="1">
-      <c r="A19" s="61"/>
-      <c r="B19" s="44"/>
-      <c r="C19" s="46"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="42"/>
-      <c r="F19" s="42"/>
-      <c r="G19" s="40"/>
+      <c r="A19" s="51"/>
+      <c r="B19" s="40"/>
+      <c r="C19" s="43"/>
+      <c r="D19" s="46"/>
+      <c r="E19" s="49"/>
+      <c r="F19" s="49"/>
+      <c r="G19" s="57"/>
       <c r="H19" s="34" t="s">
         <v>23</v>
       </c>
@@ -6157,23 +6157,23 @@
       </c>
     </row>
     <row r="20" spans="1:15">
-      <c r="A20" s="61"/>
-      <c r="B20" s="43" t="s">
+      <c r="A20" s="51"/>
+      <c r="B20" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="45" t="s">
+      <c r="C20" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="D20" s="47" t="s">
+      <c r="D20" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="E20" s="41" t="s">
+      <c r="E20" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="F20" s="41" t="s">
+      <c r="F20" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="G20" s="39" t="s">
+      <c r="G20" s="56" t="s">
         <v>13</v>
       </c>
       <c r="H20" s="33" t="s">
@@ -6202,13 +6202,13 @@
       </c>
     </row>
     <row r="21" spans="1:15">
-      <c r="A21" s="61"/>
-      <c r="B21" s="44"/>
-      <c r="C21" s="46"/>
-      <c r="D21" s="48"/>
-      <c r="E21" s="42"/>
-      <c r="F21" s="42"/>
-      <c r="G21" s="40"/>
+      <c r="A21" s="51"/>
+      <c r="B21" s="40"/>
+      <c r="C21" s="43"/>
+      <c r="D21" s="46"/>
+      <c r="E21" s="49"/>
+      <c r="F21" s="49"/>
+      <c r="G21" s="57"/>
       <c r="H21" s="31" t="s">
         <v>16</v>
       </c>
@@ -6235,13 +6235,13 @@
       </c>
     </row>
     <row r="22" spans="1:15">
-      <c r="A22" s="61"/>
-      <c r="B22" s="44"/>
-      <c r="C22" s="46"/>
-      <c r="D22" s="48"/>
-      <c r="E22" s="42"/>
-      <c r="F22" s="42"/>
-      <c r="G22" s="40"/>
+      <c r="A22" s="51"/>
+      <c r="B22" s="40"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="46"/>
+      <c r="E22" s="49"/>
+      <c r="F22" s="49"/>
+      <c r="G22" s="57"/>
       <c r="H22" s="31" t="s">
         <v>17</v>
       </c>
@@ -6268,13 +6268,13 @@
       </c>
     </row>
     <row r="23" spans="1:15">
-      <c r="A23" s="61"/>
-      <c r="B23" s="44"/>
-      <c r="C23" s="46"/>
-      <c r="D23" s="48"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="40"/>
+      <c r="A23" s="51"/>
+      <c r="B23" s="40"/>
+      <c r="C23" s="43"/>
+      <c r="D23" s="46"/>
+      <c r="E23" s="49"/>
+      <c r="F23" s="49"/>
+      <c r="G23" s="57"/>
       <c r="H23" s="31" t="s">
         <v>18</v>
       </c>
@@ -6301,13 +6301,13 @@
       </c>
     </row>
     <row r="24" spans="1:15">
-      <c r="A24" s="61"/>
-      <c r="B24" s="44"/>
-      <c r="C24" s="46"/>
-      <c r="D24" s="48"/>
-      <c r="E24" s="42"/>
-      <c r="F24" s="42"/>
-      <c r="G24" s="40"/>
+      <c r="A24" s="51"/>
+      <c r="B24" s="40"/>
+      <c r="C24" s="43"/>
+      <c r="D24" s="46"/>
+      <c r="E24" s="49"/>
+      <c r="F24" s="49"/>
+      <c r="G24" s="57"/>
       <c r="H24" s="32" t="s">
         <v>19</v>
       </c>
@@ -6334,13 +6334,13 @@
       </c>
     </row>
     <row r="25" spans="1:15">
-      <c r="A25" s="61"/>
-      <c r="B25" s="44"/>
-      <c r="C25" s="46"/>
-      <c r="D25" s="48"/>
-      <c r="E25" s="42"/>
-      <c r="F25" s="42"/>
-      <c r="G25" s="40"/>
+      <c r="A25" s="51"/>
+      <c r="B25" s="40"/>
+      <c r="C25" s="43"/>
+      <c r="D25" s="46"/>
+      <c r="E25" s="49"/>
+      <c r="F25" s="49"/>
+      <c r="G25" s="57"/>
       <c r="H25" s="31" t="s">
         <v>20</v>
       </c>
@@ -6367,13 +6367,13 @@
       </c>
     </row>
     <row r="26" spans="1:15">
-      <c r="A26" s="61"/>
-      <c r="B26" s="44"/>
-      <c r="C26" s="46"/>
-      <c r="D26" s="48"/>
-      <c r="E26" s="42"/>
-      <c r="F26" s="42"/>
-      <c r="G26" s="40"/>
+      <c r="A26" s="51"/>
+      <c r="B26" s="40"/>
+      <c r="C26" s="43"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="49"/>
+      <c r="F26" s="49"/>
+      <c r="G26" s="57"/>
       <c r="H26" s="31" t="s">
         <v>21</v>
       </c>
@@ -6400,13 +6400,13 @@
       </c>
     </row>
     <row r="27" spans="1:15">
-      <c r="A27" s="61"/>
-      <c r="B27" s="44"/>
-      <c r="C27" s="46"/>
-      <c r="D27" s="48"/>
-      <c r="E27" s="42"/>
-      <c r="F27" s="42"/>
-      <c r="G27" s="40"/>
+      <c r="A27" s="51"/>
+      <c r="B27" s="40"/>
+      <c r="C27" s="43"/>
+      <c r="D27" s="46"/>
+      <c r="E27" s="49"/>
+      <c r="F27" s="49"/>
+      <c r="G27" s="57"/>
       <c r="H27" s="31" t="s">
         <v>22</v>
       </c>
@@ -6433,13 +6433,13 @@
       </c>
     </row>
     <row r="28" spans="1:15" ht="17" thickBot="1">
-      <c r="A28" s="61"/>
-      <c r="B28" s="44"/>
-      <c r="C28" s="46"/>
-      <c r="D28" s="48"/>
-      <c r="E28" s="42"/>
-      <c r="F28" s="42"/>
-      <c r="G28" s="40"/>
+      <c r="A28" s="51"/>
+      <c r="B28" s="40"/>
+      <c r="C28" s="43"/>
+      <c r="D28" s="46"/>
+      <c r="E28" s="49"/>
+      <c r="F28" s="49"/>
+      <c r="G28" s="57"/>
       <c r="H28" s="34" t="s">
         <v>23</v>
       </c>
@@ -6466,23 +6466,23 @@
       </c>
     </row>
     <row r="29" spans="1:15">
-      <c r="A29" s="61"/>
-      <c r="B29" s="43" t="s">
+      <c r="A29" s="51"/>
+      <c r="B29" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="C29" s="45" t="s">
+      <c r="C29" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="D29" s="47" t="s">
+      <c r="D29" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="E29" s="41" t="s">
+      <c r="E29" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="F29" s="41" t="s">
+      <c r="F29" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="G29" s="39" t="s">
+      <c r="G29" s="56" t="s">
         <v>58</v>
       </c>
       <c r="H29" s="33" t="s">
@@ -6511,13 +6511,13 @@
       </c>
     </row>
     <row r="30" spans="1:15">
-      <c r="A30" s="61"/>
-      <c r="B30" s="44"/>
-      <c r="C30" s="46"/>
-      <c r="D30" s="48"/>
-      <c r="E30" s="42"/>
-      <c r="F30" s="42"/>
-      <c r="G30" s="40"/>
+      <c r="A30" s="51"/>
+      <c r="B30" s="40"/>
+      <c r="C30" s="43"/>
+      <c r="D30" s="46"/>
+      <c r="E30" s="49"/>
+      <c r="F30" s="49"/>
+      <c r="G30" s="57"/>
       <c r="H30" s="31" t="s">
         <v>16</v>
       </c>
@@ -6544,13 +6544,13 @@
       </c>
     </row>
     <row r="31" spans="1:15">
-      <c r="A31" s="61"/>
-      <c r="B31" s="44"/>
-      <c r="C31" s="46"/>
-      <c r="D31" s="48"/>
-      <c r="E31" s="42"/>
-      <c r="F31" s="42"/>
-      <c r="G31" s="40"/>
+      <c r="A31" s="51"/>
+      <c r="B31" s="40"/>
+      <c r="C31" s="43"/>
+      <c r="D31" s="46"/>
+      <c r="E31" s="49"/>
+      <c r="F31" s="49"/>
+      <c r="G31" s="57"/>
       <c r="H31" s="31" t="s">
         <v>17</v>
       </c>
@@ -6577,13 +6577,13 @@
       </c>
     </row>
     <row r="32" spans="1:15">
-      <c r="A32" s="61"/>
-      <c r="B32" s="44"/>
-      <c r="C32" s="46"/>
-      <c r="D32" s="48"/>
-      <c r="E32" s="42"/>
-      <c r="F32" s="42"/>
-      <c r="G32" s="40"/>
+      <c r="A32" s="51"/>
+      <c r="B32" s="40"/>
+      <c r="C32" s="43"/>
+      <c r="D32" s="46"/>
+      <c r="E32" s="49"/>
+      <c r="F32" s="49"/>
+      <c r="G32" s="57"/>
       <c r="H32" s="31" t="s">
         <v>18</v>
       </c>
@@ -6610,13 +6610,13 @@
       </c>
     </row>
     <row r="33" spans="1:15">
-      <c r="A33" s="61"/>
-      <c r="B33" s="44"/>
-      <c r="C33" s="46"/>
-      <c r="D33" s="48"/>
-      <c r="E33" s="42"/>
-      <c r="F33" s="42"/>
-      <c r="G33" s="40"/>
+      <c r="A33" s="51"/>
+      <c r="B33" s="40"/>
+      <c r="C33" s="43"/>
+      <c r="D33" s="46"/>
+      <c r="E33" s="49"/>
+      <c r="F33" s="49"/>
+      <c r="G33" s="57"/>
       <c r="H33" s="31" t="s">
         <v>19</v>
       </c>
@@ -6643,13 +6643,13 @@
       </c>
     </row>
     <row r="34" spans="1:15">
-      <c r="A34" s="61"/>
-      <c r="B34" s="44"/>
-      <c r="C34" s="46"/>
-      <c r="D34" s="48"/>
-      <c r="E34" s="42"/>
-      <c r="F34" s="42"/>
-      <c r="G34" s="40"/>
+      <c r="A34" s="51"/>
+      <c r="B34" s="40"/>
+      <c r="C34" s="43"/>
+      <c r="D34" s="46"/>
+      <c r="E34" s="49"/>
+      <c r="F34" s="49"/>
+      <c r="G34" s="57"/>
       <c r="H34" s="31" t="s">
         <v>20</v>
       </c>
@@ -6676,13 +6676,13 @@
       </c>
     </row>
     <row r="35" spans="1:15">
-      <c r="A35" s="61"/>
-      <c r="B35" s="44"/>
-      <c r="C35" s="46"/>
-      <c r="D35" s="48"/>
-      <c r="E35" s="42"/>
-      <c r="F35" s="42"/>
-      <c r="G35" s="40"/>
+      <c r="A35" s="51"/>
+      <c r="B35" s="40"/>
+      <c r="C35" s="43"/>
+      <c r="D35" s="46"/>
+      <c r="E35" s="49"/>
+      <c r="F35" s="49"/>
+      <c r="G35" s="57"/>
       <c r="H35" s="32" t="s">
         <v>21</v>
       </c>
@@ -6709,13 +6709,13 @@
       </c>
     </row>
     <row r="36" spans="1:15">
-      <c r="A36" s="61"/>
-      <c r="B36" s="44"/>
-      <c r="C36" s="46"/>
-      <c r="D36" s="48"/>
-      <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="40"/>
+      <c r="A36" s="51"/>
+      <c r="B36" s="40"/>
+      <c r="C36" s="43"/>
+      <c r="D36" s="46"/>
+      <c r="E36" s="49"/>
+      <c r="F36" s="49"/>
+      <c r="G36" s="57"/>
       <c r="H36" s="31" t="s">
         <v>22</v>
       </c>
@@ -6742,13 +6742,13 @@
       </c>
     </row>
     <row r="37" spans="1:15" ht="17" thickBot="1">
-      <c r="A37" s="61"/>
-      <c r="B37" s="44"/>
-      <c r="C37" s="46"/>
-      <c r="D37" s="48"/>
-      <c r="E37" s="42"/>
-      <c r="F37" s="42"/>
-      <c r="G37" s="40"/>
+      <c r="A37" s="51"/>
+      <c r="B37" s="40"/>
+      <c r="C37" s="43"/>
+      <c r="D37" s="46"/>
+      <c r="E37" s="49"/>
+      <c r="F37" s="49"/>
+      <c r="G37" s="57"/>
       <c r="H37" s="34" t="s">
         <v>23</v>
       </c>
@@ -6775,23 +6775,23 @@
       </c>
     </row>
     <row r="38" spans="1:15">
-      <c r="A38" s="61"/>
-      <c r="B38" s="43" t="s">
+      <c r="A38" s="51"/>
+      <c r="B38" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="C38" s="45" t="s">
+      <c r="C38" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="D38" s="47" t="s">
+      <c r="D38" s="45" t="s">
         <v>56</v>
       </c>
-      <c r="E38" s="41" t="s">
+      <c r="E38" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="F38" s="41" t="s">
+      <c r="F38" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="G38" s="39" t="s">
+      <c r="G38" s="56" t="s">
         <v>13</v>
       </c>
       <c r="H38" s="33" t="s">
@@ -6820,13 +6820,13 @@
       </c>
     </row>
     <row r="39" spans="1:15">
-      <c r="A39" s="61"/>
-      <c r="B39" s="44"/>
-      <c r="C39" s="46"/>
-      <c r="D39" s="48"/>
-      <c r="E39" s="42"/>
-      <c r="F39" s="42"/>
-      <c r="G39" s="40"/>
+      <c r="A39" s="51"/>
+      <c r="B39" s="40"/>
+      <c r="C39" s="43"/>
+      <c r="D39" s="46"/>
+      <c r="E39" s="49"/>
+      <c r="F39" s="49"/>
+      <c r="G39" s="57"/>
       <c r="H39" s="31" t="s">
         <v>16</v>
       </c>
@@ -6853,13 +6853,13 @@
       </c>
     </row>
     <row r="40" spans="1:15">
-      <c r="A40" s="61"/>
-      <c r="B40" s="44"/>
-      <c r="C40" s="46"/>
-      <c r="D40" s="48"/>
-      <c r="E40" s="42"/>
-      <c r="F40" s="42"/>
-      <c r="G40" s="40"/>
+      <c r="A40" s="51"/>
+      <c r="B40" s="40"/>
+      <c r="C40" s="43"/>
+      <c r="D40" s="46"/>
+      <c r="E40" s="49"/>
+      <c r="F40" s="49"/>
+      <c r="G40" s="57"/>
       <c r="H40" s="31" t="s">
         <v>17</v>
       </c>
@@ -6886,13 +6886,13 @@
       </c>
     </row>
     <row r="41" spans="1:15">
-      <c r="A41" s="61"/>
-      <c r="B41" s="44"/>
-      <c r="C41" s="46"/>
-      <c r="D41" s="48"/>
-      <c r="E41" s="42"/>
-      <c r="F41" s="42"/>
-      <c r="G41" s="40"/>
+      <c r="A41" s="51"/>
+      <c r="B41" s="40"/>
+      <c r="C41" s="43"/>
+      <c r="D41" s="46"/>
+      <c r="E41" s="49"/>
+      <c r="F41" s="49"/>
+      <c r="G41" s="57"/>
       <c r="H41" s="31" t="s">
         <v>18</v>
       </c>
@@ -6919,13 +6919,13 @@
       </c>
     </row>
     <row r="42" spans="1:15">
-      <c r="A42" s="61"/>
-      <c r="B42" s="44"/>
-      <c r="C42" s="46"/>
-      <c r="D42" s="48"/>
-      <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="40"/>
+      <c r="A42" s="51"/>
+      <c r="B42" s="40"/>
+      <c r="C42" s="43"/>
+      <c r="D42" s="46"/>
+      <c r="E42" s="49"/>
+      <c r="F42" s="49"/>
+      <c r="G42" s="57"/>
       <c r="H42" s="31" t="s">
         <v>19</v>
       </c>
@@ -6952,13 +6952,13 @@
       </c>
     </row>
     <row r="43" spans="1:15">
-      <c r="A43" s="61"/>
-      <c r="B43" s="44"/>
-      <c r="C43" s="46"/>
-      <c r="D43" s="48"/>
-      <c r="E43" s="42"/>
-      <c r="F43" s="42"/>
-      <c r="G43" s="40"/>
+      <c r="A43" s="51"/>
+      <c r="B43" s="40"/>
+      <c r="C43" s="43"/>
+      <c r="D43" s="46"/>
+      <c r="E43" s="49"/>
+      <c r="F43" s="49"/>
+      <c r="G43" s="57"/>
       <c r="H43" s="31" t="s">
         <v>20</v>
       </c>
@@ -6985,13 +6985,13 @@
       </c>
     </row>
     <row r="44" spans="1:15">
-      <c r="A44" s="61"/>
-      <c r="B44" s="44"/>
-      <c r="C44" s="46"/>
-      <c r="D44" s="48"/>
-      <c r="E44" s="42"/>
-      <c r="F44" s="42"/>
-      <c r="G44" s="40"/>
+      <c r="A44" s="51"/>
+      <c r="B44" s="40"/>
+      <c r="C44" s="43"/>
+      <c r="D44" s="46"/>
+      <c r="E44" s="49"/>
+      <c r="F44" s="49"/>
+      <c r="G44" s="57"/>
       <c r="H44" s="32" t="s">
         <v>21</v>
       </c>
@@ -7018,13 +7018,13 @@
       </c>
     </row>
     <row r="45" spans="1:15">
-      <c r="A45" s="61"/>
-      <c r="B45" s="44"/>
-      <c r="C45" s="46"/>
-      <c r="D45" s="48"/>
-      <c r="E45" s="42"/>
-      <c r="F45" s="42"/>
-      <c r="G45" s="40"/>
+      <c r="A45" s="51"/>
+      <c r="B45" s="40"/>
+      <c r="C45" s="43"/>
+      <c r="D45" s="46"/>
+      <c r="E45" s="49"/>
+      <c r="F45" s="49"/>
+      <c r="G45" s="57"/>
       <c r="H45" s="31" t="s">
         <v>22</v>
       </c>
@@ -7051,13 +7051,13 @@
       </c>
     </row>
     <row r="46" spans="1:15" ht="17" thickBot="1">
-      <c r="A46" s="61"/>
-      <c r="B46" s="44"/>
-      <c r="C46" s="46"/>
-      <c r="D46" s="48"/>
-      <c r="E46" s="42"/>
-      <c r="F46" s="42"/>
-      <c r="G46" s="40"/>
+      <c r="A46" s="51"/>
+      <c r="B46" s="40"/>
+      <c r="C46" s="43"/>
+      <c r="D46" s="46"/>
+      <c r="E46" s="49"/>
+      <c r="F46" s="49"/>
+      <c r="G46" s="57"/>
       <c r="H46" s="34" t="s">
         <v>23</v>
       </c>
@@ -7084,23 +7084,23 @@
       </c>
     </row>
     <row r="47" spans="1:15">
-      <c r="A47" s="61"/>
-      <c r="B47" s="43" t="s">
+      <c r="A47" s="51"/>
+      <c r="B47" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="C47" s="45" t="s">
+      <c r="C47" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="D47" s="47" t="s">
+      <c r="D47" s="45" t="s">
         <v>56</v>
       </c>
-      <c r="E47" s="41" t="s">
+      <c r="E47" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="F47" s="41" t="s">
+      <c r="F47" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="G47" s="39" t="s">
+      <c r="G47" s="56" t="s">
         <v>14</v>
       </c>
       <c r="H47" s="33" t="s">
@@ -7129,13 +7129,13 @@
       </c>
     </row>
     <row r="48" spans="1:15">
-      <c r="A48" s="61"/>
-      <c r="B48" s="44"/>
-      <c r="C48" s="46"/>
-      <c r="D48" s="48"/>
-      <c r="E48" s="42"/>
-      <c r="F48" s="42"/>
-      <c r="G48" s="40"/>
+      <c r="A48" s="51"/>
+      <c r="B48" s="40"/>
+      <c r="C48" s="43"/>
+      <c r="D48" s="46"/>
+      <c r="E48" s="49"/>
+      <c r="F48" s="49"/>
+      <c r="G48" s="57"/>
       <c r="H48" s="31" t="s">
         <v>16</v>
       </c>
@@ -7162,13 +7162,13 @@
       </c>
     </row>
     <row r="49" spans="1:15">
-      <c r="A49" s="61"/>
-      <c r="B49" s="44"/>
-      <c r="C49" s="46"/>
-      <c r="D49" s="48"/>
-      <c r="E49" s="42"/>
-      <c r="F49" s="42"/>
-      <c r="G49" s="40"/>
+      <c r="A49" s="51"/>
+      <c r="B49" s="40"/>
+      <c r="C49" s="43"/>
+      <c r="D49" s="46"/>
+      <c r="E49" s="49"/>
+      <c r="F49" s="49"/>
+      <c r="G49" s="57"/>
       <c r="H49" s="31" t="s">
         <v>17</v>
       </c>
@@ -7195,13 +7195,13 @@
       </c>
     </row>
     <row r="50" spans="1:15">
-      <c r="A50" s="61"/>
-      <c r="B50" s="44"/>
-      <c r="C50" s="46"/>
-      <c r="D50" s="48"/>
-      <c r="E50" s="42"/>
-      <c r="F50" s="42"/>
-      <c r="G50" s="40"/>
+      <c r="A50" s="51"/>
+      <c r="B50" s="40"/>
+      <c r="C50" s="43"/>
+      <c r="D50" s="46"/>
+      <c r="E50" s="49"/>
+      <c r="F50" s="49"/>
+      <c r="G50" s="57"/>
       <c r="H50" s="31" t="s">
         <v>18</v>
       </c>
@@ -7228,13 +7228,13 @@
       </c>
     </row>
     <row r="51" spans="1:15">
-      <c r="A51" s="61"/>
-      <c r="B51" s="44"/>
-      <c r="C51" s="46"/>
-      <c r="D51" s="48"/>
-      <c r="E51" s="42"/>
-      <c r="F51" s="42"/>
-      <c r="G51" s="40"/>
+      <c r="A51" s="51"/>
+      <c r="B51" s="40"/>
+      <c r="C51" s="43"/>
+      <c r="D51" s="46"/>
+      <c r="E51" s="49"/>
+      <c r="F51" s="49"/>
+      <c r="G51" s="57"/>
       <c r="H51" s="31" t="s">
         <v>19</v>
       </c>
@@ -7261,13 +7261,13 @@
       </c>
     </row>
     <row r="52" spans="1:15">
-      <c r="A52" s="61"/>
-      <c r="B52" s="44"/>
-      <c r="C52" s="46"/>
-      <c r="D52" s="48"/>
-      <c r="E52" s="42"/>
-      <c r="F52" s="42"/>
-      <c r="G52" s="40"/>
+      <c r="A52" s="51"/>
+      <c r="B52" s="40"/>
+      <c r="C52" s="43"/>
+      <c r="D52" s="46"/>
+      <c r="E52" s="49"/>
+      <c r="F52" s="49"/>
+      <c r="G52" s="57"/>
       <c r="H52" s="31" t="s">
         <v>20</v>
       </c>
@@ -7294,13 +7294,13 @@
       </c>
     </row>
     <row r="53" spans="1:15">
-      <c r="A53" s="61"/>
-      <c r="B53" s="44"/>
-      <c r="C53" s="46"/>
-      <c r="D53" s="48"/>
-      <c r="E53" s="42"/>
-      <c r="F53" s="42"/>
-      <c r="G53" s="40"/>
+      <c r="A53" s="51"/>
+      <c r="B53" s="40"/>
+      <c r="C53" s="43"/>
+      <c r="D53" s="46"/>
+      <c r="E53" s="49"/>
+      <c r="F53" s="49"/>
+      <c r="G53" s="57"/>
       <c r="H53" s="31" t="s">
         <v>21</v>
       </c>
@@ -7327,13 +7327,13 @@
       </c>
     </row>
     <row r="54" spans="1:15">
-      <c r="A54" s="61"/>
-      <c r="B54" s="44"/>
-      <c r="C54" s="46"/>
-      <c r="D54" s="48"/>
-      <c r="E54" s="42"/>
-      <c r="F54" s="42"/>
-      <c r="G54" s="40"/>
+      <c r="A54" s="51"/>
+      <c r="B54" s="40"/>
+      <c r="C54" s="43"/>
+      <c r="D54" s="46"/>
+      <c r="E54" s="49"/>
+      <c r="F54" s="49"/>
+      <c r="G54" s="57"/>
       <c r="H54" s="32" t="s">
         <v>22</v>
       </c>
@@ -7360,13 +7360,13 @@
       </c>
     </row>
     <row r="55" spans="1:15" ht="17" thickBot="1">
-      <c r="A55" s="62"/>
-      <c r="B55" s="44"/>
-      <c r="C55" s="46"/>
-      <c r="D55" s="48"/>
-      <c r="E55" s="42"/>
-      <c r="F55" s="42"/>
-      <c r="G55" s="40"/>
+      <c r="A55" s="52"/>
+      <c r="B55" s="40"/>
+      <c r="C55" s="43"/>
+      <c r="D55" s="46"/>
+      <c r="E55" s="49"/>
+      <c r="F55" s="49"/>
+      <c r="G55" s="57"/>
       <c r="H55" s="34" t="s">
         <v>23</v>
       </c>
@@ -7393,25 +7393,25 @@
       </c>
     </row>
     <row r="56" spans="1:15">
-      <c r="A56" s="60" t="s">
+      <c r="A56" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="B56" s="43" t="s">
+      <c r="B56" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="C56" s="45" t="s">
+      <c r="C56" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="D56" s="47" t="s">
+      <c r="D56" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="E56" s="41" t="s">
+      <c r="E56" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="F56" s="41" t="s">
+      <c r="F56" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="G56" s="39" t="s">
+      <c r="G56" s="56" t="s">
         <v>14</v>
       </c>
       <c r="H56" s="33" t="s">
@@ -7440,13 +7440,13 @@
       </c>
     </row>
     <row r="57" spans="1:15">
-      <c r="A57" s="61"/>
-      <c r="B57" s="44"/>
-      <c r="C57" s="46"/>
-      <c r="D57" s="48"/>
-      <c r="E57" s="42"/>
-      <c r="F57" s="42"/>
-      <c r="G57" s="40"/>
+      <c r="A57" s="51"/>
+      <c r="B57" s="40"/>
+      <c r="C57" s="43"/>
+      <c r="D57" s="46"/>
+      <c r="E57" s="49"/>
+      <c r="F57" s="49"/>
+      <c r="G57" s="57"/>
       <c r="H57" s="31" t="s">
         <v>16</v>
       </c>
@@ -7473,13 +7473,13 @@
       </c>
     </row>
     <row r="58" spans="1:15">
-      <c r="A58" s="61"/>
-      <c r="B58" s="44"/>
-      <c r="C58" s="46"/>
-      <c r="D58" s="48"/>
-      <c r="E58" s="42"/>
-      <c r="F58" s="42"/>
-      <c r="G58" s="40"/>
+      <c r="A58" s="51"/>
+      <c r="B58" s="40"/>
+      <c r="C58" s="43"/>
+      <c r="D58" s="46"/>
+      <c r="E58" s="49"/>
+      <c r="F58" s="49"/>
+      <c r="G58" s="57"/>
       <c r="H58" s="31" t="s">
         <v>17</v>
       </c>
@@ -7506,13 +7506,13 @@
       </c>
     </row>
     <row r="59" spans="1:15">
-      <c r="A59" s="61"/>
-      <c r="B59" s="44"/>
-      <c r="C59" s="46"/>
-      <c r="D59" s="48"/>
-      <c r="E59" s="42"/>
-      <c r="F59" s="42"/>
-      <c r="G59" s="40"/>
+      <c r="A59" s="51"/>
+      <c r="B59" s="40"/>
+      <c r="C59" s="43"/>
+      <c r="D59" s="46"/>
+      <c r="E59" s="49"/>
+      <c r="F59" s="49"/>
+      <c r="G59" s="57"/>
       <c r="H59" s="31" t="s">
         <v>18</v>
       </c>
@@ -7539,13 +7539,13 @@
       </c>
     </row>
     <row r="60" spans="1:15">
-      <c r="A60" s="61"/>
-      <c r="B60" s="44"/>
-      <c r="C60" s="46"/>
-      <c r="D60" s="48"/>
-      <c r="E60" s="42"/>
-      <c r="F60" s="42"/>
-      <c r="G60" s="40"/>
+      <c r="A60" s="51"/>
+      <c r="B60" s="40"/>
+      <c r="C60" s="43"/>
+      <c r="D60" s="46"/>
+      <c r="E60" s="49"/>
+      <c r="F60" s="49"/>
+      <c r="G60" s="57"/>
       <c r="H60" s="31" t="s">
         <v>19</v>
       </c>
@@ -7572,13 +7572,13 @@
       </c>
     </row>
     <row r="61" spans="1:15">
-      <c r="A61" s="61"/>
-      <c r="B61" s="44"/>
-      <c r="C61" s="46"/>
-      <c r="D61" s="48"/>
-      <c r="E61" s="42"/>
-      <c r="F61" s="42"/>
-      <c r="G61" s="40"/>
+      <c r="A61" s="51"/>
+      <c r="B61" s="40"/>
+      <c r="C61" s="43"/>
+      <c r="D61" s="46"/>
+      <c r="E61" s="49"/>
+      <c r="F61" s="49"/>
+      <c r="G61" s="57"/>
       <c r="H61" s="31" t="s">
         <v>20</v>
       </c>
@@ -7605,13 +7605,13 @@
       </c>
     </row>
     <row r="62" spans="1:15">
-      <c r="A62" s="61"/>
-      <c r="B62" s="44"/>
-      <c r="C62" s="46"/>
-      <c r="D62" s="48"/>
-      <c r="E62" s="42"/>
-      <c r="F62" s="42"/>
-      <c r="G62" s="40"/>
+      <c r="A62" s="51"/>
+      <c r="B62" s="40"/>
+      <c r="C62" s="43"/>
+      <c r="D62" s="46"/>
+      <c r="E62" s="49"/>
+      <c r="F62" s="49"/>
+      <c r="G62" s="57"/>
       <c r="H62" s="32" t="s">
         <v>21</v>
       </c>
@@ -7638,13 +7638,13 @@
       </c>
     </row>
     <row r="63" spans="1:15">
-      <c r="A63" s="61"/>
-      <c r="B63" s="44"/>
-      <c r="C63" s="46"/>
-      <c r="D63" s="48"/>
-      <c r="E63" s="42"/>
-      <c r="F63" s="42"/>
-      <c r="G63" s="40"/>
+      <c r="A63" s="51"/>
+      <c r="B63" s="40"/>
+      <c r="C63" s="43"/>
+      <c r="D63" s="46"/>
+      <c r="E63" s="49"/>
+      <c r="F63" s="49"/>
+      <c r="G63" s="57"/>
       <c r="H63" s="31" t="s">
         <v>22</v>
       </c>
@@ -7671,13 +7671,13 @@
       </c>
     </row>
     <row r="64" spans="1:15" ht="17" thickBot="1">
-      <c r="A64" s="61"/>
-      <c r="B64" s="44"/>
-      <c r="C64" s="46"/>
-      <c r="D64" s="48"/>
-      <c r="E64" s="42"/>
-      <c r="F64" s="42"/>
-      <c r="G64" s="40"/>
+      <c r="A64" s="51"/>
+      <c r="B64" s="40"/>
+      <c r="C64" s="43"/>
+      <c r="D64" s="46"/>
+      <c r="E64" s="49"/>
+      <c r="F64" s="49"/>
+      <c r="G64" s="57"/>
       <c r="H64" s="34" t="s">
         <v>23</v>
       </c>
@@ -7704,23 +7704,23 @@
       </c>
     </row>
     <row r="65" spans="1:15">
-      <c r="A65" s="61"/>
-      <c r="B65" s="43" t="s">
+      <c r="A65" s="51"/>
+      <c r="B65" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="C65" s="45" t="s">
+      <c r="C65" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="D65" s="47" t="s">
+      <c r="D65" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="E65" s="41" t="s">
+      <c r="E65" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="F65" s="41" t="s">
+      <c r="F65" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="G65" s="39" t="s">
+      <c r="G65" s="56" t="s">
         <v>56</v>
       </c>
       <c r="H65" s="33" t="s">
@@ -7749,13 +7749,13 @@
       </c>
     </row>
     <row r="66" spans="1:15">
-      <c r="A66" s="61"/>
-      <c r="B66" s="44"/>
-      <c r="C66" s="46"/>
-      <c r="D66" s="48"/>
-      <c r="E66" s="42"/>
-      <c r="F66" s="42"/>
-      <c r="G66" s="40"/>
+      <c r="A66" s="51"/>
+      <c r="B66" s="40"/>
+      <c r="C66" s="43"/>
+      <c r="D66" s="46"/>
+      <c r="E66" s="49"/>
+      <c r="F66" s="49"/>
+      <c r="G66" s="57"/>
       <c r="H66" s="31" t="s">
         <v>16</v>
       </c>
@@ -7782,13 +7782,13 @@
       </c>
     </row>
     <row r="67" spans="1:15">
-      <c r="A67" s="61"/>
-      <c r="B67" s="44"/>
-      <c r="C67" s="46"/>
-      <c r="D67" s="48"/>
-      <c r="E67" s="42"/>
-      <c r="F67" s="42"/>
-      <c r="G67" s="40"/>
+      <c r="A67" s="51"/>
+      <c r="B67" s="40"/>
+      <c r="C67" s="43"/>
+      <c r="D67" s="46"/>
+      <c r="E67" s="49"/>
+      <c r="F67" s="49"/>
+      <c r="G67" s="57"/>
       <c r="H67" s="31" t="s">
         <v>17</v>
       </c>
@@ -7815,13 +7815,13 @@
       </c>
     </row>
     <row r="68" spans="1:15">
-      <c r="A68" s="61"/>
-      <c r="B68" s="44"/>
-      <c r="C68" s="46"/>
-      <c r="D68" s="48"/>
-      <c r="E68" s="42"/>
-      <c r="F68" s="42"/>
-      <c r="G68" s="40"/>
+      <c r="A68" s="51"/>
+      <c r="B68" s="40"/>
+      <c r="C68" s="43"/>
+      <c r="D68" s="46"/>
+      <c r="E68" s="49"/>
+      <c r="F68" s="49"/>
+      <c r="G68" s="57"/>
       <c r="H68" s="31" t="s">
         <v>18</v>
       </c>
@@ -7848,13 +7848,13 @@
       </c>
     </row>
     <row r="69" spans="1:15">
-      <c r="A69" s="61"/>
-      <c r="B69" s="44"/>
-      <c r="C69" s="46"/>
-      <c r="D69" s="48"/>
-      <c r="E69" s="42"/>
-      <c r="F69" s="42"/>
-      <c r="G69" s="40"/>
+      <c r="A69" s="51"/>
+      <c r="B69" s="40"/>
+      <c r="C69" s="43"/>
+      <c r="D69" s="46"/>
+      <c r="E69" s="49"/>
+      <c r="F69" s="49"/>
+      <c r="G69" s="57"/>
       <c r="H69" s="32" t="s">
         <v>19</v>
       </c>
@@ -7881,13 +7881,13 @@
       </c>
     </row>
     <row r="70" spans="1:15">
-      <c r="A70" s="61"/>
-      <c r="B70" s="44"/>
-      <c r="C70" s="46"/>
-      <c r="D70" s="48"/>
-      <c r="E70" s="42"/>
-      <c r="F70" s="42"/>
-      <c r="G70" s="40"/>
+      <c r="A70" s="51"/>
+      <c r="B70" s="40"/>
+      <c r="C70" s="43"/>
+      <c r="D70" s="46"/>
+      <c r="E70" s="49"/>
+      <c r="F70" s="49"/>
+      <c r="G70" s="57"/>
       <c r="H70" s="31" t="s">
         <v>20</v>
       </c>
@@ -7914,13 +7914,13 @@
       </c>
     </row>
     <row r="71" spans="1:15">
-      <c r="A71" s="61"/>
-      <c r="B71" s="44"/>
-      <c r="C71" s="46"/>
-      <c r="D71" s="48"/>
-      <c r="E71" s="42"/>
-      <c r="F71" s="42"/>
-      <c r="G71" s="40"/>
+      <c r="A71" s="51"/>
+      <c r="B71" s="40"/>
+      <c r="C71" s="43"/>
+      <c r="D71" s="46"/>
+      <c r="E71" s="49"/>
+      <c r="F71" s="49"/>
+      <c r="G71" s="57"/>
       <c r="H71" s="31" t="s">
         <v>21</v>
       </c>
@@ -7947,13 +7947,13 @@
       </c>
     </row>
     <row r="72" spans="1:15">
-      <c r="A72" s="61"/>
-      <c r="B72" s="44"/>
-      <c r="C72" s="46"/>
-      <c r="D72" s="48"/>
-      <c r="E72" s="42"/>
-      <c r="F72" s="42"/>
-      <c r="G72" s="40"/>
+      <c r="A72" s="51"/>
+      <c r="B72" s="40"/>
+      <c r="C72" s="43"/>
+      <c r="D72" s="46"/>
+      <c r="E72" s="49"/>
+      <c r="F72" s="49"/>
+      <c r="G72" s="57"/>
       <c r="H72" s="31" t="s">
         <v>22</v>
       </c>
@@ -7980,13 +7980,13 @@
       </c>
     </row>
     <row r="73" spans="1:15" ht="17" thickBot="1">
-      <c r="A73" s="61"/>
-      <c r="B73" s="44"/>
-      <c r="C73" s="46"/>
-      <c r="D73" s="48"/>
-      <c r="E73" s="42"/>
-      <c r="F73" s="42"/>
-      <c r="G73" s="40"/>
+      <c r="A73" s="51"/>
+      <c r="B73" s="40"/>
+      <c r="C73" s="43"/>
+      <c r="D73" s="46"/>
+      <c r="E73" s="49"/>
+      <c r="F73" s="49"/>
+      <c r="G73" s="57"/>
       <c r="H73" s="31" t="s">
         <v>23</v>
       </c>
@@ -8013,23 +8013,23 @@
       </c>
     </row>
     <row r="74" spans="1:15">
-      <c r="A74" s="61"/>
-      <c r="B74" s="43" t="s">
+      <c r="A74" s="51"/>
+      <c r="B74" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="C74" s="45" t="s">
+      <c r="C74" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="D74" s="47" t="s">
+      <c r="D74" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="E74" s="41" t="s">
+      <c r="E74" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="F74" s="41" t="s">
+      <c r="F74" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="G74" s="39" t="s">
+      <c r="G74" s="56" t="s">
         <v>13</v>
       </c>
       <c r="H74" s="33" t="s">
@@ -8058,13 +8058,13 @@
       </c>
     </row>
     <row r="75" spans="1:15">
-      <c r="A75" s="61"/>
-      <c r="B75" s="44"/>
-      <c r="C75" s="46"/>
-      <c r="D75" s="48"/>
-      <c r="E75" s="42"/>
-      <c r="F75" s="42"/>
-      <c r="G75" s="40"/>
+      <c r="A75" s="51"/>
+      <c r="B75" s="40"/>
+      <c r="C75" s="43"/>
+      <c r="D75" s="46"/>
+      <c r="E75" s="49"/>
+      <c r="F75" s="49"/>
+      <c r="G75" s="57"/>
       <c r="H75" s="31" t="s">
         <v>16</v>
       </c>
@@ -8091,13 +8091,13 @@
       </c>
     </row>
     <row r="76" spans="1:15">
-      <c r="A76" s="61"/>
-      <c r="B76" s="44"/>
-      <c r="C76" s="46"/>
-      <c r="D76" s="48"/>
-      <c r="E76" s="42"/>
-      <c r="F76" s="42"/>
-      <c r="G76" s="40"/>
+      <c r="A76" s="51"/>
+      <c r="B76" s="40"/>
+      <c r="C76" s="43"/>
+      <c r="D76" s="46"/>
+      <c r="E76" s="49"/>
+      <c r="F76" s="49"/>
+      <c r="G76" s="57"/>
       <c r="H76" s="31" t="s">
         <v>17</v>
       </c>
@@ -8124,13 +8124,13 @@
       </c>
     </row>
     <row r="77" spans="1:15">
-      <c r="A77" s="61"/>
-      <c r="B77" s="44"/>
-      <c r="C77" s="46"/>
-      <c r="D77" s="48"/>
-      <c r="E77" s="42"/>
-      <c r="F77" s="42"/>
-      <c r="G77" s="40"/>
+      <c r="A77" s="51"/>
+      <c r="B77" s="40"/>
+      <c r="C77" s="43"/>
+      <c r="D77" s="46"/>
+      <c r="E77" s="49"/>
+      <c r="F77" s="49"/>
+      <c r="G77" s="57"/>
       <c r="H77" s="31" t="s">
         <v>18</v>
       </c>
@@ -8157,13 +8157,13 @@
       </c>
     </row>
     <row r="78" spans="1:15">
-      <c r="A78" s="61"/>
-      <c r="B78" s="44"/>
-      <c r="C78" s="46"/>
-      <c r="D78" s="48"/>
-      <c r="E78" s="42"/>
-      <c r="F78" s="42"/>
-      <c r="G78" s="40"/>
+      <c r="A78" s="51"/>
+      <c r="B78" s="40"/>
+      <c r="C78" s="43"/>
+      <c r="D78" s="46"/>
+      <c r="E78" s="49"/>
+      <c r="F78" s="49"/>
+      <c r="G78" s="57"/>
       <c r="H78" s="32" t="s">
         <v>19</v>
       </c>
@@ -8190,13 +8190,13 @@
       </c>
     </row>
     <row r="79" spans="1:15">
-      <c r="A79" s="61"/>
-      <c r="B79" s="44"/>
-      <c r="C79" s="46"/>
-      <c r="D79" s="48"/>
-      <c r="E79" s="42"/>
-      <c r="F79" s="42"/>
-      <c r="G79" s="40"/>
+      <c r="A79" s="51"/>
+      <c r="B79" s="40"/>
+      <c r="C79" s="43"/>
+      <c r="D79" s="46"/>
+      <c r="E79" s="49"/>
+      <c r="F79" s="49"/>
+      <c r="G79" s="57"/>
       <c r="H79" s="31" t="s">
         <v>20</v>
       </c>
@@ -8223,13 +8223,13 @@
       </c>
     </row>
     <row r="80" spans="1:15">
-      <c r="A80" s="61"/>
-      <c r="B80" s="44"/>
-      <c r="C80" s="46"/>
-      <c r="D80" s="48"/>
-      <c r="E80" s="42"/>
-      <c r="F80" s="42"/>
-      <c r="G80" s="40"/>
+      <c r="A80" s="51"/>
+      <c r="B80" s="40"/>
+      <c r="C80" s="43"/>
+      <c r="D80" s="46"/>
+      <c r="E80" s="49"/>
+      <c r="F80" s="49"/>
+      <c r="G80" s="57"/>
       <c r="H80" s="31" t="s">
         <v>21</v>
       </c>
@@ -8256,13 +8256,13 @@
       </c>
     </row>
     <row r="81" spans="1:15">
-      <c r="A81" s="61"/>
-      <c r="B81" s="44"/>
-      <c r="C81" s="46"/>
-      <c r="D81" s="48"/>
-      <c r="E81" s="42"/>
-      <c r="F81" s="42"/>
-      <c r="G81" s="40"/>
+      <c r="A81" s="51"/>
+      <c r="B81" s="40"/>
+      <c r="C81" s="43"/>
+      <c r="D81" s="46"/>
+      <c r="E81" s="49"/>
+      <c r="F81" s="49"/>
+      <c r="G81" s="57"/>
       <c r="H81" s="31" t="s">
         <v>22</v>
       </c>
@@ -8289,13 +8289,13 @@
       </c>
     </row>
     <row r="82" spans="1:15" ht="17" thickBot="1">
-      <c r="A82" s="61"/>
-      <c r="B82" s="44"/>
-      <c r="C82" s="46"/>
-      <c r="D82" s="48"/>
-      <c r="E82" s="42"/>
-      <c r="F82" s="42"/>
-      <c r="G82" s="40"/>
+      <c r="A82" s="51"/>
+      <c r="B82" s="40"/>
+      <c r="C82" s="43"/>
+      <c r="D82" s="46"/>
+      <c r="E82" s="49"/>
+      <c r="F82" s="49"/>
+      <c r="G82" s="57"/>
       <c r="H82" s="34" t="s">
         <v>23</v>
       </c>
@@ -8322,23 +8322,23 @@
       </c>
     </row>
     <row r="83" spans="1:15">
-      <c r="A83" s="61"/>
-      <c r="B83" s="43" t="s">
+      <c r="A83" s="51"/>
+      <c r="B83" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="C83" s="45" t="s">
+      <c r="C83" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="D83" s="47" t="s">
+      <c r="D83" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="E83" s="41" t="s">
+      <c r="E83" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="F83" s="41" t="s">
+      <c r="F83" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="G83" s="39" t="s">
+      <c r="G83" s="56" t="s">
         <v>58</v>
       </c>
       <c r="H83" s="33" t="s">
@@ -8367,13 +8367,13 @@
       </c>
     </row>
     <row r="84" spans="1:15">
-      <c r="A84" s="61"/>
-      <c r="B84" s="44"/>
-      <c r="C84" s="46"/>
-      <c r="D84" s="48"/>
-      <c r="E84" s="42"/>
-      <c r="F84" s="42"/>
-      <c r="G84" s="40"/>
+      <c r="A84" s="51"/>
+      <c r="B84" s="40"/>
+      <c r="C84" s="43"/>
+      <c r="D84" s="46"/>
+      <c r="E84" s="49"/>
+      <c r="F84" s="49"/>
+      <c r="G84" s="57"/>
       <c r="H84" s="31" t="s">
         <v>16</v>
       </c>
@@ -8400,13 +8400,13 @@
       </c>
     </row>
     <row r="85" spans="1:15">
-      <c r="A85" s="61"/>
-      <c r="B85" s="44"/>
-      <c r="C85" s="46"/>
-      <c r="D85" s="48"/>
-      <c r="E85" s="42"/>
-      <c r="F85" s="42"/>
-      <c r="G85" s="40"/>
+      <c r="A85" s="51"/>
+      <c r="B85" s="40"/>
+      <c r="C85" s="43"/>
+      <c r="D85" s="46"/>
+      <c r="E85" s="49"/>
+      <c r="F85" s="49"/>
+      <c r="G85" s="57"/>
       <c r="H85" s="31" t="s">
         <v>17</v>
       </c>
@@ -8433,13 +8433,13 @@
       </c>
     </row>
     <row r="86" spans="1:15">
-      <c r="A86" s="61"/>
-      <c r="B86" s="44"/>
-      <c r="C86" s="46"/>
-      <c r="D86" s="48"/>
-      <c r="E86" s="42"/>
-      <c r="F86" s="42"/>
-      <c r="G86" s="40"/>
+      <c r="A86" s="51"/>
+      <c r="B86" s="40"/>
+      <c r="C86" s="43"/>
+      <c r="D86" s="46"/>
+      <c r="E86" s="49"/>
+      <c r="F86" s="49"/>
+      <c r="G86" s="57"/>
       <c r="H86" s="31" t="s">
         <v>18</v>
       </c>
@@ -8466,13 +8466,13 @@
       </c>
     </row>
     <row r="87" spans="1:15">
-      <c r="A87" s="61"/>
-      <c r="B87" s="44"/>
-      <c r="C87" s="46"/>
-      <c r="D87" s="48"/>
-      <c r="E87" s="42"/>
-      <c r="F87" s="42"/>
-      <c r="G87" s="40"/>
+      <c r="A87" s="51"/>
+      <c r="B87" s="40"/>
+      <c r="C87" s="43"/>
+      <c r="D87" s="46"/>
+      <c r="E87" s="49"/>
+      <c r="F87" s="49"/>
+      <c r="G87" s="57"/>
       <c r="H87" s="31" t="s">
         <v>19</v>
       </c>
@@ -8499,13 +8499,13 @@
       </c>
     </row>
     <row r="88" spans="1:15">
-      <c r="A88" s="61"/>
-      <c r="B88" s="44"/>
-      <c r="C88" s="46"/>
-      <c r="D88" s="48"/>
-      <c r="E88" s="42"/>
-      <c r="F88" s="42"/>
-      <c r="G88" s="40"/>
+      <c r="A88" s="51"/>
+      <c r="B88" s="40"/>
+      <c r="C88" s="43"/>
+      <c r="D88" s="46"/>
+      <c r="E88" s="49"/>
+      <c r="F88" s="49"/>
+      <c r="G88" s="57"/>
       <c r="H88" s="31" t="s">
         <v>20</v>
       </c>
@@ -8532,13 +8532,13 @@
       </c>
     </row>
     <row r="89" spans="1:15">
-      <c r="A89" s="61"/>
-      <c r="B89" s="44"/>
-      <c r="C89" s="46"/>
-      <c r="D89" s="48"/>
-      <c r="E89" s="42"/>
-      <c r="F89" s="42"/>
-      <c r="G89" s="40"/>
+      <c r="A89" s="51"/>
+      <c r="B89" s="40"/>
+      <c r="C89" s="43"/>
+      <c r="D89" s="46"/>
+      <c r="E89" s="49"/>
+      <c r="F89" s="49"/>
+      <c r="G89" s="57"/>
       <c r="H89" s="32" t="s">
         <v>21</v>
       </c>
@@ -8565,13 +8565,13 @@
       </c>
     </row>
     <row r="90" spans="1:15">
-      <c r="A90" s="61"/>
-      <c r="B90" s="44"/>
-      <c r="C90" s="46"/>
-      <c r="D90" s="48"/>
-      <c r="E90" s="42"/>
-      <c r="F90" s="42"/>
-      <c r="G90" s="40"/>
+      <c r="A90" s="51"/>
+      <c r="B90" s="40"/>
+      <c r="C90" s="43"/>
+      <c r="D90" s="46"/>
+      <c r="E90" s="49"/>
+      <c r="F90" s="49"/>
+      <c r="G90" s="57"/>
       <c r="H90" s="31" t="s">
         <v>22</v>
       </c>
@@ -8598,13 +8598,13 @@
       </c>
     </row>
     <row r="91" spans="1:15" ht="17" thickBot="1">
-      <c r="A91" s="61"/>
-      <c r="B91" s="44"/>
-      <c r="C91" s="46"/>
-      <c r="D91" s="48"/>
-      <c r="E91" s="42"/>
-      <c r="F91" s="42"/>
-      <c r="G91" s="40"/>
+      <c r="A91" s="51"/>
+      <c r="B91" s="40"/>
+      <c r="C91" s="43"/>
+      <c r="D91" s="46"/>
+      <c r="E91" s="49"/>
+      <c r="F91" s="49"/>
+      <c r="G91" s="57"/>
       <c r="H91" s="34" t="s">
         <v>23</v>
       </c>
@@ -8631,23 +8631,23 @@
       </c>
     </row>
     <row r="92" spans="1:15">
-      <c r="A92" s="61"/>
-      <c r="B92" s="43" t="s">
+      <c r="A92" s="51"/>
+      <c r="B92" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="C92" s="45" t="s">
+      <c r="C92" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="D92" s="47" t="s">
+      <c r="D92" s="45" t="s">
         <v>56</v>
       </c>
-      <c r="E92" s="41" t="s">
+      <c r="E92" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="F92" s="41" t="s">
+      <c r="F92" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="G92" s="39" t="s">
+      <c r="G92" s="56" t="s">
         <v>13</v>
       </c>
       <c r="H92" s="33" t="s">
@@ -8676,13 +8676,13 @@
       </c>
     </row>
     <row r="93" spans="1:15">
-      <c r="A93" s="61"/>
-      <c r="B93" s="44"/>
-      <c r="C93" s="46"/>
-      <c r="D93" s="48"/>
-      <c r="E93" s="42"/>
-      <c r="F93" s="42"/>
-      <c r="G93" s="40"/>
+      <c r="A93" s="51"/>
+      <c r="B93" s="40"/>
+      <c r="C93" s="43"/>
+      <c r="D93" s="46"/>
+      <c r="E93" s="49"/>
+      <c r="F93" s="49"/>
+      <c r="G93" s="57"/>
       <c r="H93" s="31" t="s">
         <v>16</v>
       </c>
@@ -8709,13 +8709,13 @@
       </c>
     </row>
     <row r="94" spans="1:15">
-      <c r="A94" s="61"/>
-      <c r="B94" s="44"/>
-      <c r="C94" s="46"/>
-      <c r="D94" s="48"/>
-      <c r="E94" s="42"/>
-      <c r="F94" s="42"/>
-      <c r="G94" s="40"/>
+      <c r="A94" s="51"/>
+      <c r="B94" s="40"/>
+      <c r="C94" s="43"/>
+      <c r="D94" s="46"/>
+      <c r="E94" s="49"/>
+      <c r="F94" s="49"/>
+      <c r="G94" s="57"/>
       <c r="H94" s="31" t="s">
         <v>17</v>
       </c>
@@ -8742,13 +8742,13 @@
       </c>
     </row>
     <row r="95" spans="1:15">
-      <c r="A95" s="61"/>
-      <c r="B95" s="44"/>
-      <c r="C95" s="46"/>
-      <c r="D95" s="48"/>
-      <c r="E95" s="42"/>
-      <c r="F95" s="42"/>
-      <c r="G95" s="40"/>
+      <c r="A95" s="51"/>
+      <c r="B95" s="40"/>
+      <c r="C95" s="43"/>
+      <c r="D95" s="46"/>
+      <c r="E95" s="49"/>
+      <c r="F95" s="49"/>
+      <c r="G95" s="57"/>
       <c r="H95" s="31" t="s">
         <v>18</v>
       </c>
@@ -8775,13 +8775,13 @@
       </c>
     </row>
     <row r="96" spans="1:15">
-      <c r="A96" s="61"/>
-      <c r="B96" s="44"/>
-      <c r="C96" s="46"/>
-      <c r="D96" s="48"/>
-      <c r="E96" s="42"/>
-      <c r="F96" s="42"/>
-      <c r="G96" s="40"/>
+      <c r="A96" s="51"/>
+      <c r="B96" s="40"/>
+      <c r="C96" s="43"/>
+      <c r="D96" s="46"/>
+      <c r="E96" s="49"/>
+      <c r="F96" s="49"/>
+      <c r="G96" s="57"/>
       <c r="H96" s="31" t="s">
         <v>19</v>
       </c>
@@ -8808,13 +8808,13 @@
       </c>
     </row>
     <row r="97" spans="1:27">
-      <c r="A97" s="61"/>
-      <c r="B97" s="44"/>
-      <c r="C97" s="46"/>
-      <c r="D97" s="48"/>
-      <c r="E97" s="42"/>
-      <c r="F97" s="42"/>
-      <c r="G97" s="40"/>
+      <c r="A97" s="51"/>
+      <c r="B97" s="40"/>
+      <c r="C97" s="43"/>
+      <c r="D97" s="46"/>
+      <c r="E97" s="49"/>
+      <c r="F97" s="49"/>
+      <c r="G97" s="57"/>
       <c r="H97" s="31" t="s">
         <v>20</v>
       </c>
@@ -8841,13 +8841,13 @@
       </c>
     </row>
     <row r="98" spans="1:27">
-      <c r="A98" s="61"/>
-      <c r="B98" s="44"/>
-      <c r="C98" s="46"/>
-      <c r="D98" s="48"/>
-      <c r="E98" s="42"/>
-      <c r="F98" s="42"/>
-      <c r="G98" s="40"/>
+      <c r="A98" s="51"/>
+      <c r="B98" s="40"/>
+      <c r="C98" s="43"/>
+      <c r="D98" s="46"/>
+      <c r="E98" s="49"/>
+      <c r="F98" s="49"/>
+      <c r="G98" s="57"/>
       <c r="H98" s="32" t="s">
         <v>21</v>
       </c>
@@ -8874,13 +8874,13 @@
       </c>
     </row>
     <row r="99" spans="1:27">
-      <c r="A99" s="61"/>
-      <c r="B99" s="44"/>
-      <c r="C99" s="46"/>
-      <c r="D99" s="48"/>
-      <c r="E99" s="42"/>
-      <c r="F99" s="42"/>
-      <c r="G99" s="40"/>
+      <c r="A99" s="51"/>
+      <c r="B99" s="40"/>
+      <c r="C99" s="43"/>
+      <c r="D99" s="46"/>
+      <c r="E99" s="49"/>
+      <c r="F99" s="49"/>
+      <c r="G99" s="57"/>
       <c r="H99" s="31" t="s">
         <v>22</v>
       </c>
@@ -8907,13 +8907,13 @@
       </c>
     </row>
     <row r="100" spans="1:27" ht="17" thickBot="1">
-      <c r="A100" s="61"/>
-      <c r="B100" s="44"/>
-      <c r="C100" s="46"/>
-      <c r="D100" s="48"/>
-      <c r="E100" s="42"/>
-      <c r="F100" s="42"/>
-      <c r="G100" s="40"/>
+      <c r="A100" s="51"/>
+      <c r="B100" s="40"/>
+      <c r="C100" s="43"/>
+      <c r="D100" s="46"/>
+      <c r="E100" s="49"/>
+      <c r="F100" s="49"/>
+      <c r="G100" s="57"/>
       <c r="H100" s="34" t="s">
         <v>23</v>
       </c>
@@ -8940,23 +8940,23 @@
       </c>
     </row>
     <row r="101" spans="1:27">
-      <c r="A101" s="61"/>
-      <c r="B101" s="43" t="s">
+      <c r="A101" s="51"/>
+      <c r="B101" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="C101" s="45" t="s">
+      <c r="C101" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="D101" s="47" t="s">
+      <c r="D101" s="45" t="s">
         <v>56</v>
       </c>
-      <c r="E101" s="41" t="s">
+      <c r="E101" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="F101" s="41" t="s">
+      <c r="F101" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="G101" s="39" t="s">
+      <c r="G101" s="56" t="s">
         <v>14</v>
       </c>
       <c r="H101" s="33" t="s">
@@ -8985,13 +8985,13 @@
       </c>
     </row>
     <row r="102" spans="1:27">
-      <c r="A102" s="61"/>
-      <c r="B102" s="44"/>
-      <c r="C102" s="46"/>
-      <c r="D102" s="48"/>
-      <c r="E102" s="42"/>
-      <c r="F102" s="42"/>
-      <c r="G102" s="40"/>
+      <c r="A102" s="51"/>
+      <c r="B102" s="40"/>
+      <c r="C102" s="43"/>
+      <c r="D102" s="46"/>
+      <c r="E102" s="49"/>
+      <c r="F102" s="49"/>
+      <c r="G102" s="57"/>
       <c r="H102" s="31" t="s">
         <v>16</v>
       </c>
@@ -9018,13 +9018,13 @@
       </c>
     </row>
     <row r="103" spans="1:27">
-      <c r="A103" s="61"/>
-      <c r="B103" s="44"/>
-      <c r="C103" s="46"/>
-      <c r="D103" s="48"/>
-      <c r="E103" s="42"/>
-      <c r="F103" s="42"/>
-      <c r="G103" s="40"/>
+      <c r="A103" s="51"/>
+      <c r="B103" s="40"/>
+      <c r="C103" s="43"/>
+      <c r="D103" s="46"/>
+      <c r="E103" s="49"/>
+      <c r="F103" s="49"/>
+      <c r="G103" s="57"/>
       <c r="H103" s="31" t="s">
         <v>17</v>
       </c>
@@ -9051,13 +9051,13 @@
       </c>
     </row>
     <row r="104" spans="1:27">
-      <c r="A104" s="61"/>
-      <c r="B104" s="44"/>
-      <c r="C104" s="46"/>
-      <c r="D104" s="48"/>
-      <c r="E104" s="42"/>
-      <c r="F104" s="42"/>
-      <c r="G104" s="40"/>
+      <c r="A104" s="51"/>
+      <c r="B104" s="40"/>
+      <c r="C104" s="43"/>
+      <c r="D104" s="46"/>
+      <c r="E104" s="49"/>
+      <c r="F104" s="49"/>
+      <c r="G104" s="57"/>
       <c r="H104" s="31" t="s">
         <v>18</v>
       </c>
@@ -9084,13 +9084,13 @@
       </c>
     </row>
     <row r="105" spans="1:27">
-      <c r="A105" s="61"/>
-      <c r="B105" s="44"/>
-      <c r="C105" s="46"/>
-      <c r="D105" s="48"/>
-      <c r="E105" s="42"/>
-      <c r="F105" s="42"/>
-      <c r="G105" s="40"/>
+      <c r="A105" s="51"/>
+      <c r="B105" s="40"/>
+      <c r="C105" s="43"/>
+      <c r="D105" s="46"/>
+      <c r="E105" s="49"/>
+      <c r="F105" s="49"/>
+      <c r="G105" s="57"/>
       <c r="H105" s="31" t="s">
         <v>19</v>
       </c>
@@ -9117,13 +9117,13 @@
       </c>
     </row>
     <row r="106" spans="1:27">
-      <c r="A106" s="61"/>
-      <c r="B106" s="44"/>
-      <c r="C106" s="46"/>
-      <c r="D106" s="48"/>
-      <c r="E106" s="42"/>
-      <c r="F106" s="42"/>
-      <c r="G106" s="40"/>
+      <c r="A106" s="51"/>
+      <c r="B106" s="40"/>
+      <c r="C106" s="43"/>
+      <c r="D106" s="46"/>
+      <c r="E106" s="49"/>
+      <c r="F106" s="49"/>
+      <c r="G106" s="57"/>
       <c r="H106" s="31" t="s">
         <v>20</v>
       </c>
@@ -9153,13 +9153,13 @@
       </c>
     </row>
     <row r="107" spans="1:27">
-      <c r="A107" s="61"/>
-      <c r="B107" s="44"/>
-      <c r="C107" s="46"/>
-      <c r="D107" s="48"/>
-      <c r="E107" s="42"/>
-      <c r="F107" s="42"/>
-      <c r="G107" s="40"/>
+      <c r="A107" s="51"/>
+      <c r="B107" s="40"/>
+      <c r="C107" s="43"/>
+      <c r="D107" s="46"/>
+      <c r="E107" s="49"/>
+      <c r="F107" s="49"/>
+      <c r="G107" s="57"/>
       <c r="H107" s="32" t="s">
         <v>21</v>
       </c>
@@ -9186,13 +9186,13 @@
       </c>
     </row>
     <row r="108" spans="1:27">
-      <c r="A108" s="61"/>
-      <c r="B108" s="44"/>
-      <c r="C108" s="46"/>
-      <c r="D108" s="48"/>
-      <c r="E108" s="42"/>
-      <c r="F108" s="42"/>
-      <c r="G108" s="40"/>
+      <c r="A108" s="51"/>
+      <c r="B108" s="40"/>
+      <c r="C108" s="43"/>
+      <c r="D108" s="46"/>
+      <c r="E108" s="49"/>
+      <c r="F108" s="49"/>
+      <c r="G108" s="57"/>
       <c r="H108" s="31" t="s">
         <v>22</v>
       </c>
@@ -9219,13 +9219,13 @@
       </c>
     </row>
     <row r="109" spans="1:27" ht="17" thickBot="1">
-      <c r="A109" s="62"/>
-      <c r="B109" s="44"/>
-      <c r="C109" s="46"/>
-      <c r="D109" s="48"/>
-      <c r="E109" s="42"/>
-      <c r="F109" s="42"/>
-      <c r="G109" s="40"/>
+      <c r="A109" s="52"/>
+      <c r="B109" s="40"/>
+      <c r="C109" s="43"/>
+      <c r="D109" s="46"/>
+      <c r="E109" s="49"/>
+      <c r="F109" s="49"/>
+      <c r="G109" s="57"/>
       <c r="H109" s="34" t="s">
         <v>23</v>
       </c>
@@ -9252,25 +9252,25 @@
       </c>
     </row>
     <row r="110" spans="1:27">
-      <c r="A110" s="49" t="s">
+      <c r="A110" s="58" t="s">
         <v>59</v>
       </c>
-      <c r="B110" s="43" t="s">
+      <c r="B110" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="C110" s="45" t="s">
+      <c r="C110" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="D110" s="47" t="s">
+      <c r="D110" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="E110" s="41" t="s">
+      <c r="E110" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="F110" s="41" t="s">
+      <c r="F110" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="G110" s="39" t="s">
+      <c r="G110" s="56" t="s">
         <v>56</v>
       </c>
       <c r="H110" s="33" t="s">
@@ -9299,13 +9299,13 @@
       </c>
     </row>
     <row r="111" spans="1:27">
-      <c r="A111" s="50"/>
-      <c r="B111" s="44"/>
-      <c r="C111" s="46"/>
-      <c r="D111" s="48"/>
-      <c r="E111" s="42"/>
-      <c r="F111" s="42"/>
-      <c r="G111" s="40"/>
+      <c r="A111" s="59"/>
+      <c r="B111" s="40"/>
+      <c r="C111" s="43"/>
+      <c r="D111" s="46"/>
+      <c r="E111" s="49"/>
+      <c r="F111" s="49"/>
+      <c r="G111" s="57"/>
       <c r="H111" s="31" t="s">
         <v>16</v>
       </c>
@@ -9332,13 +9332,13 @@
       </c>
     </row>
     <row r="112" spans="1:27">
-      <c r="A112" s="50"/>
-      <c r="B112" s="44"/>
-      <c r="C112" s="46"/>
-      <c r="D112" s="48"/>
-      <c r="E112" s="42"/>
-      <c r="F112" s="42"/>
-      <c r="G112" s="40"/>
+      <c r="A112" s="59"/>
+      <c r="B112" s="40"/>
+      <c r="C112" s="43"/>
+      <c r="D112" s="46"/>
+      <c r="E112" s="49"/>
+      <c r="F112" s="49"/>
+      <c r="G112" s="57"/>
       <c r="H112" s="31" t="s">
         <v>17</v>
       </c>
@@ -9365,13 +9365,13 @@
       </c>
     </row>
     <row r="113" spans="1:15">
-      <c r="A113" s="50"/>
-      <c r="B113" s="44"/>
-      <c r="C113" s="46"/>
-      <c r="D113" s="48"/>
-      <c r="E113" s="42"/>
-      <c r="F113" s="42"/>
-      <c r="G113" s="40"/>
+      <c r="A113" s="59"/>
+      <c r="B113" s="40"/>
+      <c r="C113" s="43"/>
+      <c r="D113" s="46"/>
+      <c r="E113" s="49"/>
+      <c r="F113" s="49"/>
+      <c r="G113" s="57"/>
       <c r="H113" s="31" t="s">
         <v>18</v>
       </c>
@@ -9398,13 +9398,13 @@
       </c>
     </row>
     <row r="114" spans="1:15">
-      <c r="A114" s="50"/>
-      <c r="B114" s="44"/>
-      <c r="C114" s="46"/>
-      <c r="D114" s="48"/>
-      <c r="E114" s="42"/>
-      <c r="F114" s="42"/>
-      <c r="G114" s="40"/>
+      <c r="A114" s="59"/>
+      <c r="B114" s="40"/>
+      <c r="C114" s="43"/>
+      <c r="D114" s="46"/>
+      <c r="E114" s="49"/>
+      <c r="F114" s="49"/>
+      <c r="G114" s="57"/>
       <c r="H114" s="32" t="s">
         <v>19</v>
       </c>
@@ -9431,13 +9431,13 @@
       </c>
     </row>
     <row r="115" spans="1:15">
-      <c r="A115" s="50"/>
-      <c r="B115" s="44"/>
-      <c r="C115" s="46"/>
-      <c r="D115" s="48"/>
-      <c r="E115" s="42"/>
-      <c r="F115" s="42"/>
-      <c r="G115" s="40"/>
+      <c r="A115" s="59"/>
+      <c r="B115" s="40"/>
+      <c r="C115" s="43"/>
+      <c r="D115" s="46"/>
+      <c r="E115" s="49"/>
+      <c r="F115" s="49"/>
+      <c r="G115" s="57"/>
       <c r="H115" s="31" t="s">
         <v>20</v>
       </c>
@@ -9464,13 +9464,13 @@
       </c>
     </row>
     <row r="116" spans="1:15">
-      <c r="A116" s="50"/>
-      <c r="B116" s="44"/>
-      <c r="C116" s="46"/>
-      <c r="D116" s="48"/>
-      <c r="E116" s="42"/>
-      <c r="F116" s="42"/>
-      <c r="G116" s="40"/>
+      <c r="A116" s="59"/>
+      <c r="B116" s="40"/>
+      <c r="C116" s="43"/>
+      <c r="D116" s="46"/>
+      <c r="E116" s="49"/>
+      <c r="F116" s="49"/>
+      <c r="G116" s="57"/>
       <c r="H116" s="31" t="s">
         <v>21</v>
       </c>
@@ -9497,13 +9497,13 @@
       </c>
     </row>
     <row r="117" spans="1:15">
-      <c r="A117" s="50"/>
-      <c r="B117" s="44"/>
-      <c r="C117" s="46"/>
-      <c r="D117" s="48"/>
-      <c r="E117" s="42"/>
-      <c r="F117" s="42"/>
-      <c r="G117" s="40"/>
+      <c r="A117" s="59"/>
+      <c r="B117" s="40"/>
+      <c r="C117" s="43"/>
+      <c r="D117" s="46"/>
+      <c r="E117" s="49"/>
+      <c r="F117" s="49"/>
+      <c r="G117" s="57"/>
       <c r="H117" s="31" t="s">
         <v>22</v>
       </c>
@@ -9530,13 +9530,13 @@
       </c>
     </row>
     <row r="118" spans="1:15" ht="17" thickBot="1">
-      <c r="A118" s="50"/>
-      <c r="B118" s="44"/>
-      <c r="C118" s="46"/>
-      <c r="D118" s="48"/>
-      <c r="E118" s="42"/>
-      <c r="F118" s="42"/>
-      <c r="G118" s="40"/>
+      <c r="A118" s="59"/>
+      <c r="B118" s="40"/>
+      <c r="C118" s="43"/>
+      <c r="D118" s="46"/>
+      <c r="E118" s="49"/>
+      <c r="F118" s="49"/>
+      <c r="G118" s="57"/>
       <c r="H118" s="31" t="s">
         <v>23</v>
       </c>
@@ -9563,23 +9563,23 @@
       </c>
     </row>
     <row r="119" spans="1:15">
-      <c r="A119" s="50"/>
-      <c r="B119" s="43" t="s">
+      <c r="A119" s="59"/>
+      <c r="B119" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="C119" s="45" t="s">
+      <c r="C119" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="D119" s="47" t="s">
+      <c r="D119" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="E119" s="41" t="s">
+      <c r="E119" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="F119" s="41" t="s">
+      <c r="F119" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="G119" s="39" t="s">
+      <c r="G119" s="56" t="s">
         <v>58</v>
       </c>
       <c r="H119" s="33" t="s">
@@ -9608,13 +9608,13 @@
       </c>
     </row>
     <row r="120" spans="1:15">
-      <c r="A120" s="50"/>
-      <c r="B120" s="44"/>
-      <c r="C120" s="46"/>
-      <c r="D120" s="48"/>
-      <c r="E120" s="42"/>
-      <c r="F120" s="42"/>
-      <c r="G120" s="40"/>
+      <c r="A120" s="59"/>
+      <c r="B120" s="40"/>
+      <c r="C120" s="43"/>
+      <c r="D120" s="46"/>
+      <c r="E120" s="49"/>
+      <c r="F120" s="49"/>
+      <c r="G120" s="57"/>
       <c r="H120" s="31" t="s">
         <v>16</v>
       </c>
@@ -9641,13 +9641,13 @@
       </c>
     </row>
     <row r="121" spans="1:15">
-      <c r="A121" s="50"/>
-      <c r="B121" s="44"/>
-      <c r="C121" s="46"/>
-      <c r="D121" s="48"/>
-      <c r="E121" s="42"/>
-      <c r="F121" s="42"/>
-      <c r="G121" s="40"/>
+      <c r="A121" s="59"/>
+      <c r="B121" s="40"/>
+      <c r="C121" s="43"/>
+      <c r="D121" s="46"/>
+      <c r="E121" s="49"/>
+      <c r="F121" s="49"/>
+      <c r="G121" s="57"/>
       <c r="H121" s="31" t="s">
         <v>17</v>
       </c>
@@ -9674,13 +9674,13 @@
       </c>
     </row>
     <row r="122" spans="1:15">
-      <c r="A122" s="50"/>
-      <c r="B122" s="44"/>
-      <c r="C122" s="46"/>
-      <c r="D122" s="48"/>
-      <c r="E122" s="42"/>
-      <c r="F122" s="42"/>
-      <c r="G122" s="40"/>
+      <c r="A122" s="59"/>
+      <c r="B122" s="40"/>
+      <c r="C122" s="43"/>
+      <c r="D122" s="46"/>
+      <c r="E122" s="49"/>
+      <c r="F122" s="49"/>
+      <c r="G122" s="57"/>
       <c r="H122" s="31" t="s">
         <v>18</v>
       </c>
@@ -9707,13 +9707,13 @@
       </c>
     </row>
     <row r="123" spans="1:15">
-      <c r="A123" s="50"/>
-      <c r="B123" s="44"/>
-      <c r="C123" s="46"/>
-      <c r="D123" s="48"/>
-      <c r="E123" s="42"/>
-      <c r="F123" s="42"/>
-      <c r="G123" s="40"/>
+      <c r="A123" s="59"/>
+      <c r="B123" s="40"/>
+      <c r="C123" s="43"/>
+      <c r="D123" s="46"/>
+      <c r="E123" s="49"/>
+      <c r="F123" s="49"/>
+      <c r="G123" s="57"/>
       <c r="H123" s="31" t="s">
         <v>19</v>
       </c>
@@ -9740,13 +9740,13 @@
       </c>
     </row>
     <row r="124" spans="1:15">
-      <c r="A124" s="50"/>
-      <c r="B124" s="44"/>
-      <c r="C124" s="46"/>
-      <c r="D124" s="48"/>
-      <c r="E124" s="42"/>
-      <c r="F124" s="42"/>
-      <c r="G124" s="40"/>
+      <c r="A124" s="59"/>
+      <c r="B124" s="40"/>
+      <c r="C124" s="43"/>
+      <c r="D124" s="46"/>
+      <c r="E124" s="49"/>
+      <c r="F124" s="49"/>
+      <c r="G124" s="57"/>
       <c r="H124" s="31" t="s">
         <v>20</v>
       </c>
@@ -9773,13 +9773,13 @@
       </c>
     </row>
     <row r="125" spans="1:15">
-      <c r="A125" s="50"/>
-      <c r="B125" s="44"/>
-      <c r="C125" s="46"/>
-      <c r="D125" s="48"/>
-      <c r="E125" s="42"/>
-      <c r="F125" s="42"/>
-      <c r="G125" s="40"/>
+      <c r="A125" s="59"/>
+      <c r="B125" s="40"/>
+      <c r="C125" s="43"/>
+      <c r="D125" s="46"/>
+      <c r="E125" s="49"/>
+      <c r="F125" s="49"/>
+      <c r="G125" s="57"/>
       <c r="H125" s="32" t="s">
         <v>21</v>
       </c>
@@ -9806,13 +9806,13 @@
       </c>
     </row>
     <row r="126" spans="1:15">
-      <c r="A126" s="50"/>
-      <c r="B126" s="44"/>
-      <c r="C126" s="46"/>
-      <c r="D126" s="48"/>
-      <c r="E126" s="42"/>
-      <c r="F126" s="42"/>
-      <c r="G126" s="40"/>
+      <c r="A126" s="59"/>
+      <c r="B126" s="40"/>
+      <c r="C126" s="43"/>
+      <c r="D126" s="46"/>
+      <c r="E126" s="49"/>
+      <c r="F126" s="49"/>
+      <c r="G126" s="57"/>
       <c r="H126" s="31" t="s">
         <v>22</v>
       </c>
@@ -9839,13 +9839,13 @@
       </c>
     </row>
     <row r="127" spans="1:15" ht="17" thickBot="1">
-      <c r="A127" s="50"/>
-      <c r="B127" s="44"/>
-      <c r="C127" s="46"/>
-      <c r="D127" s="48"/>
-      <c r="E127" s="42"/>
-      <c r="F127" s="42"/>
-      <c r="G127" s="40"/>
+      <c r="A127" s="59"/>
+      <c r="B127" s="40"/>
+      <c r="C127" s="43"/>
+      <c r="D127" s="46"/>
+      <c r="E127" s="49"/>
+      <c r="F127" s="49"/>
+      <c r="G127" s="57"/>
       <c r="H127" s="34" t="s">
         <v>23</v>
       </c>
@@ -9872,23 +9872,23 @@
       </c>
     </row>
     <row r="128" spans="1:15">
-      <c r="A128" s="50"/>
-      <c r="B128" s="43" t="s">
+      <c r="A128" s="59"/>
+      <c r="B128" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="C128" s="45" t="s">
+      <c r="C128" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="D128" s="47" t="s">
+      <c r="D128" s="45" t="s">
         <v>56</v>
       </c>
-      <c r="E128" s="41" t="s">
+      <c r="E128" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="F128" s="41" t="s">
+      <c r="F128" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="G128" s="39" t="s">
+      <c r="G128" s="56" t="s">
         <v>13</v>
       </c>
       <c r="H128" s="33" t="s">
@@ -9917,13 +9917,13 @@
       </c>
     </row>
     <row r="129" spans="1:15">
-      <c r="A129" s="50"/>
-      <c r="B129" s="44"/>
-      <c r="C129" s="46"/>
-      <c r="D129" s="48"/>
-      <c r="E129" s="42"/>
-      <c r="F129" s="42"/>
-      <c r="G129" s="40"/>
+      <c r="A129" s="59"/>
+      <c r="B129" s="40"/>
+      <c r="C129" s="43"/>
+      <c r="D129" s="46"/>
+      <c r="E129" s="49"/>
+      <c r="F129" s="49"/>
+      <c r="G129" s="57"/>
       <c r="H129" s="31" t="s">
         <v>16</v>
       </c>
@@ -9950,13 +9950,13 @@
       </c>
     </row>
     <row r="130" spans="1:15">
-      <c r="A130" s="50"/>
-      <c r="B130" s="44"/>
-      <c r="C130" s="46"/>
-      <c r="D130" s="48"/>
-      <c r="E130" s="42"/>
-      <c r="F130" s="42"/>
-      <c r="G130" s="40"/>
+      <c r="A130" s="59"/>
+      <c r="B130" s="40"/>
+      <c r="C130" s="43"/>
+      <c r="D130" s="46"/>
+      <c r="E130" s="49"/>
+      <c r="F130" s="49"/>
+      <c r="G130" s="57"/>
       <c r="H130" s="31" t="s">
         <v>17</v>
       </c>
@@ -9983,13 +9983,13 @@
       </c>
     </row>
     <row r="131" spans="1:15">
-      <c r="A131" s="50"/>
-      <c r="B131" s="44"/>
-      <c r="C131" s="46"/>
-      <c r="D131" s="48"/>
-      <c r="E131" s="42"/>
-      <c r="F131" s="42"/>
-      <c r="G131" s="40"/>
+      <c r="A131" s="59"/>
+      <c r="B131" s="40"/>
+      <c r="C131" s="43"/>
+      <c r="D131" s="46"/>
+      <c r="E131" s="49"/>
+      <c r="F131" s="49"/>
+      <c r="G131" s="57"/>
       <c r="H131" s="31" t="s">
         <v>18</v>
       </c>
@@ -10016,13 +10016,13 @@
       </c>
     </row>
     <row r="132" spans="1:15">
-      <c r="A132" s="50"/>
-      <c r="B132" s="44"/>
-      <c r="C132" s="46"/>
-      <c r="D132" s="48"/>
-      <c r="E132" s="42"/>
-      <c r="F132" s="42"/>
-      <c r="G132" s="40"/>
+      <c r="A132" s="59"/>
+      <c r="B132" s="40"/>
+      <c r="C132" s="43"/>
+      <c r="D132" s="46"/>
+      <c r="E132" s="49"/>
+      <c r="F132" s="49"/>
+      <c r="G132" s="57"/>
       <c r="H132" s="31" t="s">
         <v>19</v>
       </c>
@@ -10049,13 +10049,13 @@
       </c>
     </row>
     <row r="133" spans="1:15">
-      <c r="A133" s="50"/>
-      <c r="B133" s="44"/>
-      <c r="C133" s="46"/>
-      <c r="D133" s="48"/>
-      <c r="E133" s="42"/>
-      <c r="F133" s="42"/>
-      <c r="G133" s="40"/>
+      <c r="A133" s="59"/>
+      <c r="B133" s="40"/>
+      <c r="C133" s="43"/>
+      <c r="D133" s="46"/>
+      <c r="E133" s="49"/>
+      <c r="F133" s="49"/>
+      <c r="G133" s="57"/>
       <c r="H133" s="31" t="s">
         <v>20</v>
       </c>
@@ -10082,13 +10082,13 @@
       </c>
     </row>
     <row r="134" spans="1:15">
-      <c r="A134" s="50"/>
-      <c r="B134" s="44"/>
-      <c r="C134" s="46"/>
-      <c r="D134" s="48"/>
-      <c r="E134" s="42"/>
-      <c r="F134" s="42"/>
-      <c r="G134" s="40"/>
+      <c r="A134" s="59"/>
+      <c r="B134" s="40"/>
+      <c r="C134" s="43"/>
+      <c r="D134" s="46"/>
+      <c r="E134" s="49"/>
+      <c r="F134" s="49"/>
+      <c r="G134" s="57"/>
       <c r="H134" s="31" t="s">
         <v>21</v>
       </c>
@@ -10115,13 +10115,13 @@
       </c>
     </row>
     <row r="135" spans="1:15">
-      <c r="A135" s="50"/>
-      <c r="B135" s="44"/>
-      <c r="C135" s="46"/>
-      <c r="D135" s="48"/>
-      <c r="E135" s="42"/>
-      <c r="F135" s="42"/>
-      <c r="G135" s="40"/>
+      <c r="A135" s="59"/>
+      <c r="B135" s="40"/>
+      <c r="C135" s="43"/>
+      <c r="D135" s="46"/>
+      <c r="E135" s="49"/>
+      <c r="F135" s="49"/>
+      <c r="G135" s="57"/>
       <c r="H135" s="32" t="s">
         <v>22</v>
       </c>
@@ -10148,13 +10148,13 @@
       </c>
     </row>
     <row r="136" spans="1:15" ht="17" thickBot="1">
-      <c r="A136" s="50"/>
-      <c r="B136" s="44"/>
-      <c r="C136" s="46"/>
-      <c r="D136" s="48"/>
-      <c r="E136" s="42"/>
-      <c r="F136" s="42"/>
-      <c r="G136" s="40"/>
+      <c r="A136" s="59"/>
+      <c r="B136" s="40"/>
+      <c r="C136" s="43"/>
+      <c r="D136" s="46"/>
+      <c r="E136" s="49"/>
+      <c r="F136" s="49"/>
+      <c r="G136" s="57"/>
       <c r="H136" s="31" t="s">
         <v>23</v>
       </c>
@@ -10181,23 +10181,23 @@
       </c>
     </row>
     <row r="137" spans="1:15">
-      <c r="A137" s="50"/>
-      <c r="B137" s="43" t="s">
+      <c r="A137" s="59"/>
+      <c r="B137" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="C137" s="45" t="s">
+      <c r="C137" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="D137" s="47" t="s">
+      <c r="D137" s="45" t="s">
         <v>56</v>
       </c>
-      <c r="E137" s="41" t="s">
+      <c r="E137" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="F137" s="41" t="s">
+      <c r="F137" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="G137" s="39" t="s">
+      <c r="G137" s="56" t="s">
         <v>14</v>
       </c>
       <c r="H137" s="35" t="s">
@@ -10226,13 +10226,13 @@
       </c>
     </row>
     <row r="138" spans="1:15">
-      <c r="A138" s="50"/>
-      <c r="B138" s="44"/>
-      <c r="C138" s="46"/>
-      <c r="D138" s="48"/>
-      <c r="E138" s="42"/>
-      <c r="F138" s="42"/>
-      <c r="G138" s="40"/>
+      <c r="A138" s="59"/>
+      <c r="B138" s="40"/>
+      <c r="C138" s="43"/>
+      <c r="D138" s="46"/>
+      <c r="E138" s="49"/>
+      <c r="F138" s="49"/>
+      <c r="G138" s="57"/>
       <c r="H138" s="36" t="s">
         <v>16</v>
       </c>
@@ -10259,13 +10259,13 @@
       </c>
     </row>
     <row r="139" spans="1:15">
-      <c r="A139" s="50"/>
-      <c r="B139" s="44"/>
-      <c r="C139" s="46"/>
-      <c r="D139" s="48"/>
-      <c r="E139" s="42"/>
-      <c r="F139" s="42"/>
-      <c r="G139" s="40"/>
+      <c r="A139" s="59"/>
+      <c r="B139" s="40"/>
+      <c r="C139" s="43"/>
+      <c r="D139" s="46"/>
+      <c r="E139" s="49"/>
+      <c r="F139" s="49"/>
+      <c r="G139" s="57"/>
       <c r="H139" s="36" t="s">
         <v>17</v>
       </c>
@@ -10292,13 +10292,13 @@
       </c>
     </row>
     <row r="140" spans="1:15">
-      <c r="A140" s="50"/>
-      <c r="B140" s="44"/>
-      <c r="C140" s="46"/>
-      <c r="D140" s="48"/>
-      <c r="E140" s="42"/>
-      <c r="F140" s="42"/>
-      <c r="G140" s="40"/>
+      <c r="A140" s="59"/>
+      <c r="B140" s="40"/>
+      <c r="C140" s="43"/>
+      <c r="D140" s="46"/>
+      <c r="E140" s="49"/>
+      <c r="F140" s="49"/>
+      <c r="G140" s="57"/>
       <c r="H140" s="36" t="s">
         <v>18</v>
       </c>
@@ -10325,13 +10325,13 @@
       </c>
     </row>
     <row r="141" spans="1:15">
-      <c r="A141" s="50"/>
-      <c r="B141" s="44"/>
-      <c r="C141" s="46"/>
-      <c r="D141" s="48"/>
-      <c r="E141" s="42"/>
-      <c r="F141" s="42"/>
-      <c r="G141" s="40"/>
+      <c r="A141" s="59"/>
+      <c r="B141" s="40"/>
+      <c r="C141" s="43"/>
+      <c r="D141" s="46"/>
+      <c r="E141" s="49"/>
+      <c r="F141" s="49"/>
+      <c r="G141" s="57"/>
       <c r="H141" s="36" t="s">
         <v>19</v>
       </c>
@@ -10358,13 +10358,13 @@
       </c>
     </row>
     <row r="142" spans="1:15">
-      <c r="A142" s="50"/>
-      <c r="B142" s="44"/>
-      <c r="C142" s="46"/>
-      <c r="D142" s="48"/>
-      <c r="E142" s="42"/>
-      <c r="F142" s="42"/>
-      <c r="G142" s="40"/>
+      <c r="A142" s="59"/>
+      <c r="B142" s="40"/>
+      <c r="C142" s="43"/>
+      <c r="D142" s="46"/>
+      <c r="E142" s="49"/>
+      <c r="F142" s="49"/>
+      <c r="G142" s="57"/>
       <c r="H142" s="36" t="s">
         <v>20</v>
       </c>
@@ -10391,13 +10391,13 @@
       </c>
     </row>
     <row r="143" spans="1:15">
-      <c r="A143" s="50"/>
-      <c r="B143" s="44"/>
-      <c r="C143" s="46"/>
-      <c r="D143" s="48"/>
-      <c r="E143" s="42"/>
-      <c r="F143" s="42"/>
-      <c r="G143" s="40"/>
+      <c r="A143" s="59"/>
+      <c r="B143" s="40"/>
+      <c r="C143" s="43"/>
+      <c r="D143" s="46"/>
+      <c r="E143" s="49"/>
+      <c r="F143" s="49"/>
+      <c r="G143" s="57"/>
       <c r="H143" s="38" t="s">
         <v>21</v>
       </c>
@@ -10424,13 +10424,13 @@
       </c>
     </row>
     <row r="144" spans="1:15">
-      <c r="A144" s="50"/>
-      <c r="B144" s="44"/>
-      <c r="C144" s="46"/>
-      <c r="D144" s="48"/>
-      <c r="E144" s="42"/>
-      <c r="F144" s="42"/>
-      <c r="G144" s="40"/>
+      <c r="A144" s="59"/>
+      <c r="B144" s="40"/>
+      <c r="C144" s="43"/>
+      <c r="D144" s="46"/>
+      <c r="E144" s="49"/>
+      <c r="F144" s="49"/>
+      <c r="G144" s="57"/>
       <c r="H144" s="36" t="s">
         <v>22</v>
       </c>
@@ -10457,13 +10457,13 @@
       </c>
     </row>
     <row r="145" spans="1:15" ht="17" thickBot="1">
-      <c r="A145" s="51"/>
-      <c r="B145" s="57"/>
-      <c r="C145" s="58"/>
-      <c r="D145" s="59"/>
-      <c r="E145" s="52"/>
-      <c r="F145" s="52"/>
-      <c r="G145" s="53"/>
+      <c r="A145" s="60"/>
+      <c r="B145" s="41"/>
+      <c r="C145" s="44"/>
+      <c r="D145" s="47"/>
+      <c r="E145" s="61"/>
+      <c r="F145" s="61"/>
+      <c r="G145" s="62"/>
       <c r="H145" s="37" t="s">
         <v>23</v>
       </c>
@@ -10491,41 +10491,48 @@
     </row>
   </sheetData>
   <mergeCells count="101">
-    <mergeCell ref="B137:B145"/>
-    <mergeCell ref="C137:C145"/>
-    <mergeCell ref="D137:D145"/>
-    <mergeCell ref="D38:D46"/>
-    <mergeCell ref="E38:E46"/>
-    <mergeCell ref="A2:A55"/>
-    <mergeCell ref="B11:B19"/>
-    <mergeCell ref="C11:C19"/>
-    <mergeCell ref="D11:D19"/>
-    <mergeCell ref="E11:E19"/>
-    <mergeCell ref="E119:E127"/>
-    <mergeCell ref="E128:E136"/>
-    <mergeCell ref="A56:A109"/>
-    <mergeCell ref="C101:C109"/>
-    <mergeCell ref="D101:D109"/>
-    <mergeCell ref="B83:B91"/>
-    <mergeCell ref="C83:C91"/>
-    <mergeCell ref="D83:D91"/>
-    <mergeCell ref="E83:E91"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="B2:B10"/>
-    <mergeCell ref="C2:C10"/>
-    <mergeCell ref="D2:D10"/>
-    <mergeCell ref="E2:E10"/>
-    <mergeCell ref="F2:F10"/>
-    <mergeCell ref="G2:G10"/>
-    <mergeCell ref="B20:B28"/>
-    <mergeCell ref="C20:C28"/>
-    <mergeCell ref="D20:D28"/>
-    <mergeCell ref="E20:E28"/>
-    <mergeCell ref="F20:F28"/>
-    <mergeCell ref="G20:G28"/>
-    <mergeCell ref="F11:F19"/>
-    <mergeCell ref="G11:G19"/>
+    <mergeCell ref="G29:G37"/>
+    <mergeCell ref="F29:F37"/>
+    <mergeCell ref="E29:E37"/>
+    <mergeCell ref="B29:B37"/>
+    <mergeCell ref="C29:C37"/>
+    <mergeCell ref="D29:D37"/>
+    <mergeCell ref="B38:B46"/>
+    <mergeCell ref="C38:C46"/>
+    <mergeCell ref="F83:F91"/>
+    <mergeCell ref="G83:G91"/>
+    <mergeCell ref="F38:F46"/>
+    <mergeCell ref="G38:G46"/>
+    <mergeCell ref="B47:B55"/>
+    <mergeCell ref="C47:C55"/>
+    <mergeCell ref="D47:D55"/>
+    <mergeCell ref="E47:E55"/>
+    <mergeCell ref="F47:F55"/>
+    <mergeCell ref="G47:G55"/>
+    <mergeCell ref="F128:F136"/>
+    <mergeCell ref="G128:G136"/>
+    <mergeCell ref="A110:A145"/>
+    <mergeCell ref="G74:G82"/>
+    <mergeCell ref="B128:B136"/>
+    <mergeCell ref="C128:C136"/>
+    <mergeCell ref="D128:D136"/>
+    <mergeCell ref="E101:E109"/>
+    <mergeCell ref="F101:F109"/>
+    <mergeCell ref="G101:G109"/>
+    <mergeCell ref="B74:B82"/>
+    <mergeCell ref="C74:C82"/>
+    <mergeCell ref="D74:D82"/>
+    <mergeCell ref="E74:E82"/>
+    <mergeCell ref="F74:F82"/>
+    <mergeCell ref="E137:E145"/>
+    <mergeCell ref="G137:G145"/>
+    <mergeCell ref="F137:F145"/>
+    <mergeCell ref="E110:E118"/>
+    <mergeCell ref="G110:G118"/>
+    <mergeCell ref="B119:B127"/>
+    <mergeCell ref="C119:C127"/>
+    <mergeCell ref="D119:D127"/>
+    <mergeCell ref="B92:B100"/>
     <mergeCell ref="F119:F127"/>
     <mergeCell ref="G119:G127"/>
     <mergeCell ref="F110:F118"/>
@@ -10550,48 +10557,41 @@
     <mergeCell ref="F92:F100"/>
     <mergeCell ref="G92:G100"/>
     <mergeCell ref="B101:B109"/>
-    <mergeCell ref="F128:F136"/>
-    <mergeCell ref="G128:G136"/>
-    <mergeCell ref="A110:A145"/>
-    <mergeCell ref="G74:G82"/>
-    <mergeCell ref="B128:B136"/>
-    <mergeCell ref="C128:C136"/>
-    <mergeCell ref="D128:D136"/>
-    <mergeCell ref="E101:E109"/>
-    <mergeCell ref="F101:F109"/>
-    <mergeCell ref="G101:G109"/>
-    <mergeCell ref="B74:B82"/>
-    <mergeCell ref="C74:C82"/>
-    <mergeCell ref="D74:D82"/>
-    <mergeCell ref="E74:E82"/>
-    <mergeCell ref="F74:F82"/>
-    <mergeCell ref="E137:E145"/>
-    <mergeCell ref="G137:G145"/>
-    <mergeCell ref="F137:F145"/>
-    <mergeCell ref="E110:E118"/>
-    <mergeCell ref="G110:G118"/>
-    <mergeCell ref="B119:B127"/>
-    <mergeCell ref="C119:C127"/>
-    <mergeCell ref="D119:D127"/>
-    <mergeCell ref="B92:B100"/>
-    <mergeCell ref="G29:G37"/>
-    <mergeCell ref="F29:F37"/>
-    <mergeCell ref="E29:E37"/>
-    <mergeCell ref="B29:B37"/>
-    <mergeCell ref="C29:C37"/>
-    <mergeCell ref="D29:D37"/>
-    <mergeCell ref="B38:B46"/>
-    <mergeCell ref="C38:C46"/>
-    <mergeCell ref="F83:F91"/>
-    <mergeCell ref="G83:G91"/>
-    <mergeCell ref="F38:F46"/>
-    <mergeCell ref="G38:G46"/>
-    <mergeCell ref="B47:B55"/>
-    <mergeCell ref="C47:C55"/>
-    <mergeCell ref="D47:D55"/>
-    <mergeCell ref="E47:E55"/>
-    <mergeCell ref="F47:F55"/>
-    <mergeCell ref="G47:G55"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="B2:B10"/>
+    <mergeCell ref="C2:C10"/>
+    <mergeCell ref="D2:D10"/>
+    <mergeCell ref="E2:E10"/>
+    <mergeCell ref="F2:F10"/>
+    <mergeCell ref="G2:G10"/>
+    <mergeCell ref="B20:B28"/>
+    <mergeCell ref="C20:C28"/>
+    <mergeCell ref="D20:D28"/>
+    <mergeCell ref="E20:E28"/>
+    <mergeCell ref="F20:F28"/>
+    <mergeCell ref="G20:G28"/>
+    <mergeCell ref="F11:F19"/>
+    <mergeCell ref="G11:G19"/>
+    <mergeCell ref="B137:B145"/>
+    <mergeCell ref="C137:C145"/>
+    <mergeCell ref="D137:D145"/>
+    <mergeCell ref="D38:D46"/>
+    <mergeCell ref="E38:E46"/>
+    <mergeCell ref="A2:A55"/>
+    <mergeCell ref="B11:B19"/>
+    <mergeCell ref="C11:C19"/>
+    <mergeCell ref="D11:D19"/>
+    <mergeCell ref="E11:E19"/>
+    <mergeCell ref="E119:E127"/>
+    <mergeCell ref="E128:E136"/>
+    <mergeCell ref="A56:A109"/>
+    <mergeCell ref="C101:C109"/>
+    <mergeCell ref="D101:D109"/>
+    <mergeCell ref="B83:B91"/>
+    <mergeCell ref="C83:C91"/>
+    <mergeCell ref="D83:D91"/>
+    <mergeCell ref="E83:E91"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
